--- a/experiments/敦煌变化数据_90d.xlsx
+++ b/experiments/敦煌变化数据_90d.xlsx
@@ -13136,139 +13136,139 @@
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>46.65</v>
+        <v>45.02</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>35</v>
+        <v>33.85</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>18.43</v>
+        <v>17.82</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>46.54</v>
+        <v>46.73</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>36.37</v>
+        <v>37.01</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>17.1</v>
+        <v>13.25</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>47</v>
+        <v>44.63</v>
       </c>
       <c r="I5" s="26" t="n">
-        <v>34.41</v>
+        <v>31.7</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>18.57</v>
+        <v>16.37</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>58.4</v>
+        <v>55.5</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-32.28</v>
+        <v>-33.39</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>14.63</v>
+        <v>13.41</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>58.52</v>
+        <v>56.99</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>-33.41</v>
+        <v>-35.5</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>15.6</v>
+        <v>17.36</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>61.03</v>
+        <v>65.2</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>-31.48</v>
+        <v>-30.33</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>15.96</v>
+        <v>15.91</v>
       </c>
       <c r="T5" s="26" t="n">
-        <v>40.68</v>
+        <v>39.22</v>
       </c>
       <c r="U5" s="26" t="n">
-        <v>-5.27</v>
+        <v>-5.2</v>
       </c>
       <c r="V5" s="26" t="n">
-        <v>-31.95</v>
+        <v>-30.33</v>
       </c>
       <c r="W5" s="26" t="n">
-        <v>40.62</v>
+        <v>40.84</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>-5.75</v>
+        <v>-7.39</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>-33.11</v>
+        <v>-33.1</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>40.53</v>
+        <v>40.36</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>-5.34</v>
+        <v>-5.14</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>-33.78</v>
+        <v>-36.94</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>49.07</v>
+        <v>48.81</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>35.02</v>
+        <v>32.82</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>20.16</v>
+        <v>15.91</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>50.2</v>
+        <v>47.19</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>34.35</v>
+        <v>33.5</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>19.18</v>
+        <v>15.12</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>61.09</v>
+        <v>63.69</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>-30.84</v>
+        <v>-28.17</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>14.89</v>
+        <v>13.17</v>
       </c>
       <c r="AL5" s="26" t="n">
-        <v>62.67</v>
+        <v>62.32</v>
       </c>
       <c r="AM5" s="26" t="n">
-        <v>-30.93</v>
+        <v>-31.85</v>
       </c>
       <c r="AN5" s="26" t="n">
-        <v>14.02</v>
+        <v>14.27</v>
       </c>
       <c r="AO5" s="26" t="n">
-        <v>38.22</v>
+        <v>32.23</v>
       </c>
       <c r="AP5" s="26" t="n">
-        <v>-6.71</v>
+        <v>-11.97</v>
       </c>
       <c r="AQ5" s="26" t="n">
-        <v>-26.67</v>
+        <v>-22.04</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>36.86</v>
+        <v>32.36</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>-7.76</v>
+        <v>-11.25</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>-26.64</v>
+        <v>-23.37</v>
       </c>
     </row>
     <row r="6">
@@ -13278,139 +13278,139 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>46.95</v>
+        <v>45.93</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>35.12</v>
+        <v>34.22</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>17.91</v>
+        <v>16.26</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>46.23</v>
+        <v>45.77</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>36.53</v>
+        <v>37.5</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>17.7</v>
+        <v>15.07</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>46.93</v>
+        <v>44.43</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>34.68</v>
+        <v>32.53</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>16.84</v>
+        <v>11.14</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>59.31</v>
+        <v>58.28</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-31.89</v>
+        <v>-32.23</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>15.1</v>
+        <v>14.81</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>58.15</v>
+        <v>55.87</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>-32.26</v>
+        <v>-32</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>15.63</v>
+        <v>17.43</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>59.95</v>
+        <v>61.91</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>-31.44</v>
+        <v>-30.2</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>12.06</v>
+        <v>4.1</v>
       </c>
       <c r="T6" s="26" t="n">
-        <v>44.02</v>
+        <v>49.33</v>
       </c>
       <c r="U6" s="26" t="n">
-        <v>-5.67</v>
+        <v>-6.4</v>
       </c>
       <c r="V6" s="26" t="n">
-        <v>-33.35</v>
+        <v>-34.58</v>
       </c>
       <c r="W6" s="26" t="n">
-        <v>40.13</v>
+        <v>39.37</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>-5.81</v>
+        <v>-7.59</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>-32.85</v>
+        <v>-32.31</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>40.77</v>
+        <v>41.09</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>-5.65</v>
+        <v>-6.06</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>-37.2</v>
+        <v>-47.32</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>48.54</v>
+        <v>47.18</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>35.03</v>
+        <v>32.86</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>21.48</v>
+        <v>19.9</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>50.26</v>
+        <v>47.37</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>33.6</v>
+        <v>31.23</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>18.75</v>
+        <v>13.81</v>
       </c>
       <c r="AI6" s="26" t="n">
-        <v>61.45</v>
+        <v>64.78</v>
       </c>
       <c r="AJ6" s="26" t="n">
-        <v>-30.21</v>
+        <v>-26.26</v>
       </c>
       <c r="AK6" s="26" t="n">
-        <v>15.1</v>
+        <v>13.82</v>
       </c>
       <c r="AL6" s="26" t="n">
-        <v>62.68</v>
+        <v>62.37</v>
       </c>
       <c r="AM6" s="26" t="n">
-        <v>-30.66</v>
+        <v>-31.04</v>
       </c>
       <c r="AN6" s="26" t="n">
-        <v>14</v>
+        <v>14.21</v>
       </c>
       <c r="AO6" s="26" t="n">
-        <v>39.86</v>
+        <v>37.19</v>
       </c>
       <c r="AP6" s="26" t="n">
-        <v>-6.32</v>
+        <v>-10.81</v>
       </c>
       <c r="AQ6" s="26" t="n">
-        <v>-25.45</v>
+        <v>-18.34</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>40.87</v>
+        <v>44.51</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>-7.18</v>
+        <v>-9.48</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>-29.37</v>
+        <v>-31.64</v>
       </c>
     </row>
     <row r="7">
@@ -13420,139 +13420,139 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>47.35</v>
+        <v>47.14</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>34.36</v>
+        <v>31.91</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>17.98</v>
+        <v>16.45</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>46.11</v>
+        <v>45.41</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>35.95</v>
+        <v>35.75</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>16.24</v>
+        <v>10.62</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>47.26</v>
+        <v>45.45</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>34.04</v>
+        <v>30.58</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>17.57</v>
+        <v>13.34</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>58.91</v>
+        <v>57.07</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-31.72</v>
+        <v>-31.71</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>15.36</v>
+        <v>15.62</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>58.21</v>
+        <v>56.07</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>-32.54</v>
+        <v>-32.87</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>16.21</v>
+        <v>19.21</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>57.64</v>
+        <v>54.93</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>-32.06</v>
+        <v>-32.07</v>
       </c>
       <c r="S7" s="26" t="n">
-        <v>16.55</v>
+        <v>17.72</v>
       </c>
       <c r="T7" s="26" t="n">
-        <v>39.58</v>
+        <v>35.88</v>
       </c>
       <c r="U7" s="26" t="n">
-        <v>-5.23</v>
+        <v>-5.09</v>
       </c>
       <c r="V7" s="26" t="n">
-        <v>-31.83</v>
+        <v>-29.96</v>
       </c>
       <c r="W7" s="26" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="X7" s="26" t="n">
-        <v>-5.75</v>
+        <v>-7.41</v>
       </c>
       <c r="Y7" s="26" t="n">
-        <v>-32.61</v>
+        <v>-31.6</v>
       </c>
       <c r="Z7" s="26" t="n">
-        <v>41</v>
+        <v>41.8</v>
       </c>
       <c r="AA7" s="26" t="n">
-        <v>-5.15</v>
+        <v>-4.55</v>
       </c>
       <c r="AB7" s="26" t="n">
-        <v>-33.59</v>
+        <v>-36.36</v>
       </c>
       <c r="AC7" s="26" t="n">
-        <v>49.55</v>
+        <v>50.27</v>
       </c>
       <c r="AD7" s="26" t="n">
-        <v>34.21</v>
+        <v>30.36</v>
       </c>
       <c r="AE7" s="26" t="n">
-        <v>19.86</v>
+        <v>15</v>
       </c>
       <c r="AF7" s="26" t="n">
-        <v>51.64</v>
+        <v>51.57</v>
       </c>
       <c r="AG7" s="26" t="n">
-        <v>33.66</v>
+        <v>31.4</v>
       </c>
       <c r="AH7" s="26" t="n">
-        <v>19.6</v>
+        <v>16.38</v>
       </c>
       <c r="AI7" s="26" t="n">
-        <v>61.86</v>
+        <v>66.03</v>
       </c>
       <c r="AJ7" s="26" t="n">
-        <v>-31.57</v>
+        <v>-30.37</v>
       </c>
       <c r="AK7" s="26" t="n">
-        <v>15.32</v>
+        <v>14.49</v>
       </c>
       <c r="AL7" s="26" t="n">
-        <v>62.64</v>
+        <v>62.24</v>
       </c>
       <c r="AM7" s="26" t="n">
-        <v>-30.83</v>
+        <v>-31.55</v>
       </c>
       <c r="AN7" s="26" t="n">
-        <v>14.55</v>
+        <v>15.86</v>
       </c>
       <c r="AO7" s="26" t="n">
-        <v>38.54</v>
+        <v>33.2</v>
       </c>
       <c r="AP7" s="26" t="n">
-        <v>-4.42</v>
+        <v>-5.03</v>
       </c>
       <c r="AQ7" s="26" t="n">
-        <v>-26.15</v>
+        <v>-20.45</v>
       </c>
       <c r="AR7" s="26" t="n">
-        <v>38.4</v>
+        <v>37.01</v>
       </c>
       <c r="AS7" s="26" t="n">
-        <v>-7.98</v>
+        <v>-11.93</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-29.78</v>
+        <v>-32.89</v>
       </c>
     </row>
     <row r="8">
@@ -13562,139 +13562,139 @@
         </is>
       </c>
       <c r="B8" s="26" t="n">
-        <v>46.89</v>
+        <v>45.77</v>
       </c>
       <c r="C8" s="26" t="n">
-        <v>33.41</v>
+        <v>29.05</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>17.44</v>
+        <v>14.83</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>45.89</v>
+        <v>44.75</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>35.2</v>
+        <v>33.49</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>16.8</v>
+        <v>12.34</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>47.47</v>
+        <v>46.07</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>34.59</v>
+        <v>32.25</v>
       </c>
       <c r="J8" s="26" t="n">
-        <v>16.45</v>
+        <v>9.94</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>60.46</v>
+        <v>61.77</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-30.89</v>
+        <v>-29.18</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>14.94</v>
+        <v>14.34</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>57.95</v>
+        <v>55.26</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>-32.25</v>
+        <v>-32</v>
       </c>
       <c r="P8" s="26" t="n">
-        <v>15.91</v>
+        <v>18.28</v>
       </c>
       <c r="Q8" s="26" t="n">
-        <v>60</v>
+        <v>62.07</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>-31.33</v>
+        <v>-29.85</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>16.23</v>
+        <v>16.73</v>
       </c>
       <c r="T8" s="26" t="n">
-        <v>42.78</v>
+        <v>45.57</v>
       </c>
       <c r="U8" s="26" t="n">
-        <v>-5.46</v>
+        <v>-5.78</v>
       </c>
       <c r="V8" s="26" t="n">
-        <v>-33.19</v>
+        <v>-34.08</v>
       </c>
       <c r="W8" s="26" t="n">
-        <v>40.74</v>
+        <v>41.21</v>
       </c>
       <c r="X8" s="26" t="n">
-        <v>-5.53</v>
+        <v>-6.72</v>
       </c>
       <c r="Y8" s="26" t="n">
-        <v>-32.74</v>
+        <v>-31.97</v>
       </c>
       <c r="Z8" s="26" t="n">
-        <v>41.12</v>
+        <v>42.16</v>
       </c>
       <c r="AA8" s="26" t="n">
-        <v>-5.31</v>
+        <v>-5.04</v>
       </c>
       <c r="AB8" s="26" t="n">
-        <v>-32.98</v>
+        <v>-34.54</v>
       </c>
       <c r="AC8" s="26" t="n">
-        <v>48.57</v>
+        <v>47.28</v>
       </c>
       <c r="AD8" s="26" t="n">
-        <v>32.7</v>
+        <v>25.8</v>
       </c>
       <c r="AE8" s="26" t="n">
-        <v>19.22</v>
+        <v>13.06</v>
       </c>
       <c r="AF8" s="26" t="n">
-        <v>50.63</v>
+        <v>48.51</v>
       </c>
       <c r="AG8" s="26" t="n">
-        <v>34</v>
+        <v>32.45</v>
       </c>
       <c r="AH8" s="26" t="n">
-        <v>19.43</v>
+        <v>15.88</v>
       </c>
       <c r="AI8" s="26" t="n">
-        <v>61.9</v>
+        <v>66.16</v>
       </c>
       <c r="AJ8" s="26" t="n">
-        <v>-31.36</v>
+        <v>-29.73</v>
       </c>
       <c r="AK8" s="26" t="n">
-        <v>13.93</v>
+        <v>10.27</v>
       </c>
       <c r="AL8" s="26" t="n">
-        <v>62.66</v>
+        <v>62.29</v>
       </c>
       <c r="AM8" s="26" t="n">
-        <v>-30.63</v>
+        <v>-30.96</v>
       </c>
       <c r="AN8" s="26" t="n">
-        <v>13.81</v>
+        <v>13.63</v>
       </c>
       <c r="AO8" s="26" t="n">
-        <v>38.14</v>
+        <v>32</v>
       </c>
       <c r="AP8" s="26" t="n">
-        <v>-7.4</v>
+        <v>-14.06</v>
       </c>
       <c r="AQ8" s="26" t="n">
-        <v>-26.18</v>
+        <v>-20.56</v>
       </c>
       <c r="AR8" s="26" t="n">
-        <v>39.64</v>
+        <v>40.78</v>
       </c>
       <c r="AS8" s="26" t="n">
-        <v>-6.63</v>
+        <v>-7.82</v>
       </c>
       <c r="AT8" s="26" t="n">
-        <v>-27.95</v>
+        <v>-27.35</v>
       </c>
     </row>
     <row r="9">
@@ -13704,139 +13704,139 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>46.54</v>
+        <v>44.68</v>
       </c>
       <c r="C9" s="26" t="n">
-        <v>34.89</v>
+        <v>33.53</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>17.36</v>
+        <v>14.57</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>45.88</v>
+        <v>44.73</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>35.45</v>
+        <v>34.24</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>17.16</v>
+        <v>13.43</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>46.44</v>
+        <v>42.95</v>
       </c>
       <c r="I9" s="26" t="n">
-        <v>34.41</v>
+        <v>31.72</v>
       </c>
       <c r="J9" s="26" t="n">
-        <v>16.61</v>
+        <v>10.42</v>
       </c>
       <c r="K9" s="26" t="n">
-        <v>60.16</v>
+        <v>60.84</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-31.35</v>
+        <v>-30.59</v>
       </c>
       <c r="M9" s="26" t="n">
-        <v>15.19</v>
+        <v>15.1</v>
       </c>
       <c r="N9" s="26" t="n">
-        <v>57.42</v>
+        <v>53.66</v>
       </c>
       <c r="O9" s="26" t="n">
-        <v>-32.72</v>
+        <v>-33.42</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>16.09</v>
+        <v>18.83</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>59.42</v>
+        <v>60.31</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>-31.28</v>
+        <v>-29.72</v>
       </c>
       <c r="S9" s="26" t="n">
-        <v>14.87</v>
+        <v>12.61</v>
       </c>
       <c r="T9" s="26" t="n">
-        <v>41.81</v>
+        <v>42.65</v>
       </c>
       <c r="U9" s="26" t="n">
-        <v>-6.19</v>
+        <v>-8.01</v>
       </c>
       <c r="V9" s="26" t="n">
-        <v>-30.5</v>
+        <v>-25.92</v>
       </c>
       <c r="W9" s="26" t="n">
-        <v>40.99</v>
+        <v>41.97</v>
       </c>
       <c r="X9" s="26" t="n">
-        <v>-5.24</v>
+        <v>-5.84</v>
       </c>
       <c r="Y9" s="26" t="n">
-        <v>-31.85</v>
+        <v>-29.28</v>
       </c>
       <c r="Z9" s="26" t="n">
-        <v>40.72</v>
+        <v>40.96</v>
       </c>
       <c r="AA9" s="26" t="n">
-        <v>-6.28</v>
+        <v>-7.99</v>
       </c>
       <c r="AB9" s="26" t="n">
-        <v>-34.31</v>
+        <v>-38.56</v>
       </c>
       <c r="AC9" s="26" t="n">
-        <v>49.45</v>
+        <v>49.96</v>
       </c>
       <c r="AD9" s="26" t="n">
-        <v>33.37</v>
+        <v>27.83</v>
       </c>
       <c r="AE9" s="26" t="n">
-        <v>17.07</v>
+        <v>6.54</v>
       </c>
       <c r="AF9" s="26" t="n">
-        <v>51.03</v>
+        <v>49.71</v>
       </c>
       <c r="AG9" s="26" t="n">
-        <v>33.7</v>
+        <v>31.53</v>
       </c>
       <c r="AH9" s="26" t="n">
-        <v>20.09</v>
+        <v>17.87</v>
       </c>
       <c r="AI9" s="26" t="n">
-        <v>61.93</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AJ9" s="26" t="n">
-        <v>-30.51</v>
+        <v>-27.15</v>
       </c>
       <c r="AK9" s="26" t="n">
-        <v>13.43</v>
+        <v>8.76</v>
       </c>
       <c r="AL9" s="26" t="n">
-        <v>62.87</v>
+        <v>62.92</v>
       </c>
       <c r="AM9" s="26" t="n">
-        <v>-30.81</v>
+        <v>-31.51</v>
       </c>
       <c r="AN9" s="26" t="n">
-        <v>14.76</v>
+        <v>16.52</v>
       </c>
       <c r="AO9" s="26" t="n">
-        <v>38.93</v>
+        <v>34.37</v>
       </c>
       <c r="AP9" s="26" t="n">
-        <v>-4.65</v>
+        <v>-5.74</v>
       </c>
       <c r="AQ9" s="26" t="n">
-        <v>-26.96</v>
+        <v>-22.91</v>
       </c>
       <c r="AR9" s="26" t="n">
-        <v>37.84</v>
+        <v>35.33</v>
       </c>
       <c r="AS9" s="26" t="n">
-        <v>-8.1</v>
+        <v>-12.3</v>
       </c>
       <c r="AT9" s="26" t="n">
-        <v>-29.12</v>
+        <v>-30.89</v>
       </c>
     </row>
     <row r="10">
@@ -13846,139 +13846,139 @@
         </is>
       </c>
       <c r="B10" s="26" t="n">
-        <v>46.88</v>
+        <v>45.72</v>
       </c>
       <c r="C10" s="26" t="n">
-        <v>33.34</v>
+        <v>28.84</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>17.21</v>
+        <v>14.13</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>45.62</v>
+        <v>43.93</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>35.85</v>
+        <v>35.43</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>15.83</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>46.99</v>
+        <v>44.61</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>34.81</v>
+        <v>32.93</v>
       </c>
       <c r="J10" s="26" t="n">
-        <v>14.87</v>
+        <v>5.17</v>
       </c>
       <c r="K10" s="26" t="n">
-        <v>59.96</v>
+        <v>60.25</v>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-32.02</v>
+        <v>-32.6</v>
       </c>
       <c r="M10" s="26" t="n">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>58.26</v>
+        <v>56.2</v>
       </c>
       <c r="O10" s="26" t="n">
-        <v>-31.75</v>
+        <v>-30.47</v>
       </c>
       <c r="P10" s="26" t="n">
-        <v>16.57</v>
+        <v>20.3</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>58.9</v>
+        <v>58.75</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>-29.8</v>
+        <v>-25.22</v>
       </c>
       <c r="S10" s="26" t="n">
-        <v>16.46</v>
+        <v>17.44</v>
       </c>
       <c r="T10" s="26" t="n">
-        <v>43.14</v>
+        <v>46.67</v>
       </c>
       <c r="U10" s="26" t="n">
-        <v>-5.58</v>
+        <v>-6.15</v>
       </c>
       <c r="V10" s="26" t="n">
-        <v>-30.41</v>
+        <v>-25.65</v>
       </c>
       <c r="W10" s="26" t="n">
-        <v>40.44</v>
+        <v>40.3</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>-4.34</v>
+        <v>-3.12</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>-33.63</v>
+        <v>-34.68</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>41.51</v>
+        <v>43.33</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>-4.16</v>
+        <v>-1.57</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>-33.4</v>
+        <v>-35.8</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>49.62</v>
+        <v>50.48</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>32.31</v>
+        <v>24.6</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>18.33</v>
+        <v>10.35</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>50.26</v>
+        <v>47.36</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>33.49</v>
+        <v>30.88</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>17.85</v>
+        <v>11.07</v>
       </c>
       <c r="AI10" s="26" t="n">
-        <v>61.27</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AJ10" s="26" t="n">
-        <v>-29.63</v>
+        <v>-24.5</v>
       </c>
       <c r="AK10" s="26" t="n">
-        <v>12.3</v>
+        <v>5.33</v>
       </c>
       <c r="AL10" s="26" t="n">
-        <v>62.79</v>
+        <v>62.69</v>
       </c>
       <c r="AM10" s="26" t="n">
-        <v>-30.86</v>
+        <v>-31.65</v>
       </c>
       <c r="AN10" s="26" t="n">
-        <v>14.53</v>
+        <v>15.8</v>
       </c>
       <c r="AO10" s="26" t="n">
-        <v>40.96</v>
+        <v>40.55</v>
       </c>
       <c r="AP10" s="26" t="n">
-        <v>-6.88</v>
+        <v>-12.5</v>
       </c>
       <c r="AQ10" s="26" t="n">
-        <v>-26.41</v>
+        <v>-21.26</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>39.45</v>
+        <v>40.21</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>-7.07</v>
+        <v>-9.17</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>-28.96</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="11">
@@ -13988,139 +13988,139 @@
         </is>
       </c>
       <c r="B11" s="26" t="n">
-        <v>46.47</v>
+        <v>44.47</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>33.32</v>
+        <v>28.78</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>16.8</v>
+        <v>12.89</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>45.7</v>
+        <v>44.16</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>35.43</v>
+        <v>34.17</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>15.44</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>46.88</v>
+        <v>44.28</v>
       </c>
       <c r="I11" s="26" t="n">
-        <v>33.73</v>
+        <v>29.66</v>
       </c>
       <c r="J11" s="26" t="n">
-        <v>15.72</v>
+        <v>7.73</v>
       </c>
       <c r="K11" s="26" t="n">
-        <v>60.59</v>
+        <v>62.16</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-31.36</v>
+        <v>-30.59</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>15.02</v>
+        <v>14.57</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>58.9</v>
+        <v>58.15</v>
       </c>
       <c r="O11" s="26" t="n">
-        <v>-31.78</v>
+        <v>-30.55</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>15.44</v>
+        <v>16.86</v>
       </c>
       <c r="Q11" s="26" t="n">
-        <v>59.3</v>
+        <v>59.94</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>-30.92</v>
+        <v>-28.63</v>
       </c>
       <c r="S11" s="26" t="n">
-        <v>10.83</v>
+        <v>0.36</v>
       </c>
       <c r="T11" s="26" t="n">
-        <v>43.12</v>
+        <v>46.62</v>
       </c>
       <c r="U11" s="26" t="n">
-        <v>-5.82</v>
+        <v>-6.87</v>
       </c>
       <c r="V11" s="26" t="n">
-        <v>-30.91</v>
+        <v>-27.17</v>
       </c>
       <c r="W11" s="26" t="n">
-        <v>40.5</v>
+        <v>40.49</v>
       </c>
       <c r="X11" s="26" t="n">
-        <v>-4.99</v>
+        <v>-5.11</v>
       </c>
       <c r="Y11" s="26" t="n">
-        <v>-32.82</v>
+        <v>-32.23</v>
       </c>
       <c r="Z11" s="26" t="n">
-        <v>41.43</v>
+        <v>43.11</v>
       </c>
       <c r="AA11" s="26" t="n">
-        <v>-4.55</v>
+        <v>-2.73</v>
       </c>
       <c r="AB11" s="26" t="n">
-        <v>-30.09</v>
+        <v>-25.76</v>
       </c>
       <c r="AC11" s="26" t="n">
-        <v>49.36</v>
+        <v>49.69</v>
       </c>
       <c r="AD11" s="26" t="n">
-        <v>31.95</v>
+        <v>23.52</v>
       </c>
       <c r="AE11" s="26" t="n">
-        <v>16.57</v>
+        <v>5.02</v>
       </c>
       <c r="AF11" s="26" t="n">
-        <v>50.27</v>
+        <v>47.4</v>
       </c>
       <c r="AG11" s="26" t="n">
-        <v>33.04</v>
+        <v>29.54</v>
       </c>
       <c r="AH11" s="26" t="n">
-        <v>19.46</v>
+        <v>15.98</v>
       </c>
       <c r="AI11" s="26" t="n">
-        <v>61.25</v>
+        <v>64.17</v>
       </c>
       <c r="AJ11" s="26" t="n">
-        <v>-29.39</v>
+        <v>-23.77</v>
       </c>
       <c r="AK11" s="26" t="n">
-        <v>13.23</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AL11" s="26" t="n">
-        <v>62.92</v>
+        <v>63.07</v>
       </c>
       <c r="AM11" s="26" t="n">
-        <v>-30.59</v>
+        <v>-30.84</v>
       </c>
       <c r="AN11" s="26" t="n">
-        <v>14.62</v>
+        <v>16.08</v>
       </c>
       <c r="AO11" s="26" t="n">
-        <v>40.71</v>
+        <v>39.79</v>
       </c>
       <c r="AP11" s="26" t="n">
-        <v>-5.15</v>
+        <v>-7.23</v>
       </c>
       <c r="AQ11" s="26" t="n">
-        <v>-25.19</v>
+        <v>-17.54</v>
       </c>
       <c r="AR11" s="26" t="n">
-        <v>39.58</v>
+        <v>40.58</v>
       </c>
       <c r="AS11" s="26" t="n">
-        <v>-8.19</v>
+        <v>-12.55</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-29.4</v>
+        <v>-31.73</v>
       </c>
     </row>
     <row r="12">
@@ -14130,139 +14130,139 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>46.4</v>
+        <v>44.26</v>
       </c>
       <c r="C12" s="26" t="n">
-        <v>33.57</v>
+        <v>29.53</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>16.64</v>
+        <v>12.41</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>45.2</v>
+        <v>42.65</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>34.7</v>
+        <v>31.96</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>15.48</v>
+        <v>8.34</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>47.33</v>
+        <v>45.65</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>33.99</v>
+        <v>30.42</v>
       </c>
       <c r="J12" s="26" t="n">
-        <v>12.46</v>
+        <v>-2.16</v>
       </c>
       <c r="K12" s="26" t="n">
-        <v>59.85</v>
+        <v>59.92</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-32.07</v>
+        <v>-32.76</v>
       </c>
       <c r="M12" s="26" t="n">
-        <v>15.13</v>
+        <v>14.89</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>58.01</v>
+        <v>55.44</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>-31.9</v>
+        <v>-30.92</v>
       </c>
       <c r="P12" s="26" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>60.56</v>
+        <v>63.78</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>-29.45</v>
+        <v>-24.16</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>12.56</v>
+        <v>5.61</v>
       </c>
       <c r="T12" s="26" t="n">
-        <v>42.22</v>
+        <v>43.89</v>
       </c>
       <c r="U12" s="26" t="n">
-        <v>-6.35</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="V12" s="26" t="n">
-        <v>-30.98</v>
+        <v>-27.39</v>
       </c>
       <c r="W12" s="26" t="n">
-        <v>40.84</v>
+        <v>41.51</v>
       </c>
       <c r="X12" s="26" t="n">
-        <v>-4.69</v>
+        <v>-4.18</v>
       </c>
       <c r="Y12" s="26" t="n">
-        <v>-32.46</v>
+        <v>-31.13</v>
       </c>
       <c r="Z12" s="26" t="n">
-        <v>41.82</v>
+        <v>44.27</v>
       </c>
       <c r="AA12" s="26" t="n">
-        <v>-5.14</v>
+        <v>-4.52</v>
       </c>
       <c r="AB12" s="26" t="n">
-        <v>-31.29</v>
+        <v>-29.4</v>
       </c>
       <c r="AC12" s="26" t="n">
-        <v>49.93</v>
+        <v>51.4</v>
       </c>
       <c r="AD12" s="26" t="n">
-        <v>31.8</v>
+        <v>23.05</v>
       </c>
       <c r="AE12" s="26" t="n">
-        <v>16.29</v>
+        <v>4.17</v>
       </c>
       <c r="AF12" s="26" t="n">
-        <v>51.2</v>
+        <v>50.23</v>
       </c>
       <c r="AG12" s="26" t="n">
-        <v>33.26</v>
+        <v>30.18</v>
       </c>
       <c r="AH12" s="26" t="n">
-        <v>19.23</v>
+        <v>15.27</v>
       </c>
       <c r="AI12" s="26" t="n">
-        <v>62.02</v>
+        <v>66.5</v>
       </c>
       <c r="AJ12" s="26" t="n">
-        <v>-28.83</v>
+        <v>-22.06</v>
       </c>
       <c r="AK12" s="26" t="n">
-        <v>14.07</v>
+        <v>10.7</v>
       </c>
       <c r="AL12" s="26" t="n">
-        <v>62.82</v>
+        <v>62.79</v>
       </c>
       <c r="AM12" s="26" t="n">
-        <v>-30.51</v>
+        <v>-30.59</v>
       </c>
       <c r="AN12" s="26" t="n">
-        <v>14.14</v>
+        <v>14.62</v>
       </c>
       <c r="AO12" s="26" t="n">
-        <v>39.97</v>
+        <v>37.55</v>
       </c>
       <c r="AP12" s="26" t="n">
-        <v>-8.26</v>
+        <v>-16.66</v>
       </c>
       <c r="AQ12" s="26" t="n">
-        <v>-28.37</v>
+        <v>-27.18</v>
       </c>
       <c r="AR12" s="26" t="n">
-        <v>36.58</v>
+        <v>31.5</v>
       </c>
       <c r="AS12" s="26" t="n">
-        <v>-7.33</v>
+        <v>-9.94</v>
       </c>
       <c r="AT12" s="26" t="n">
-        <v>-29.11</v>
+        <v>-30.87</v>
       </c>
     </row>
     <row r="13">
@@ -14272,139 +14272,139 @@
         </is>
       </c>
       <c r="B13" s="26" t="n">
-        <v>46.22</v>
+        <v>43.72</v>
       </c>
       <c r="C13" s="26" t="n">
-        <v>34.12</v>
+        <v>31.19</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>16.21</v>
+        <v>11.1</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>45.27</v>
+        <v>42.88</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>34.82</v>
+        <v>32.33</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>16.1</v>
+        <v>10.21</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>46.72</v>
+        <v>43.79</v>
       </c>
       <c r="I13" s="26" t="n">
-        <v>33.58</v>
+        <v>29.2</v>
       </c>
       <c r="J13" s="26" t="n">
-        <v>14.8</v>
+        <v>4.94</v>
       </c>
       <c r="K13" s="26" t="n">
-        <v>60.58</v>
+        <v>62.12</v>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-31.12</v>
+        <v>-29.88</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>14.79</v>
+        <v>13.86</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>58.05</v>
+        <v>55.58</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>-32.13</v>
+        <v>-31.61</v>
       </c>
       <c r="P13" s="26" t="n">
-        <v>16.51</v>
+        <v>20.12</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>61.71</v>
+        <v>67.27</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>-29.15</v>
+        <v>-23.26</v>
       </c>
       <c r="S13" s="26" t="n">
-        <v>12.13</v>
+        <v>4.3</v>
       </c>
       <c r="T13" s="26" t="n">
-        <v>43.56</v>
+        <v>47.96</v>
       </c>
       <c r="U13" s="26" t="n">
-        <v>-6.54</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="V13" s="26" t="n">
-        <v>-29.16</v>
+        <v>-21.87</v>
       </c>
       <c r="W13" s="26" t="n">
-        <v>41.05</v>
+        <v>42.16</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>-4.53</v>
+        <v>-3.69</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>-32.19</v>
+        <v>-30.33</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>41.72</v>
+        <v>43.96</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>-4.95</v>
+        <v>-3.95</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>-33.62</v>
+        <v>-36.45</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>50.37</v>
+        <v>52.75</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>29.98</v>
+        <v>17.55</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>15.59</v>
+        <v>2.05</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>50</v>
+        <v>46.59</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>32.87</v>
+        <v>29.01</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>18.48</v>
+        <v>13.01</v>
       </c>
       <c r="AI13" s="26" t="n">
-        <v>62.58</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AJ13" s="26" t="n">
-        <v>-29.66</v>
+        <v>-24.57</v>
       </c>
       <c r="AK13" s="26" t="n">
-        <v>12.64</v>
+        <v>6.35</v>
       </c>
       <c r="AL13" s="26" t="n">
-        <v>62.97</v>
+        <v>63.23</v>
       </c>
       <c r="AM13" s="26" t="n">
-        <v>-30.52</v>
+        <v>-30.61</v>
       </c>
       <c r="AN13" s="26" t="n">
-        <v>14.25</v>
+        <v>14.95</v>
       </c>
       <c r="AO13" s="26" t="n">
-        <v>38.11</v>
+        <v>31.89</v>
       </c>
       <c r="AP13" s="26" t="n">
-        <v>-6.14</v>
+        <v>-10.24</v>
       </c>
       <c r="AQ13" s="26" t="n">
-        <v>-26.98</v>
+        <v>-22.99</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>42.45</v>
+        <v>49.29</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>-6.36</v>
+        <v>-7.01</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-27.86</v>
+        <v>-27.06</v>
       </c>
     </row>
     <row r="14">
@@ -14414,139 +14414,139 @@
         </is>
       </c>
       <c r="B14" s="26" t="n">
-        <v>47.06</v>
+        <v>46.26</v>
       </c>
       <c r="C14" s="26" t="n">
-        <v>33.59</v>
+        <v>29.6</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>16.02</v>
+        <v>10.52</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>45.23</v>
+        <v>42.76</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>34.09</v>
+        <v>30.11</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>15.23</v>
+        <v>7.56</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>46.84</v>
+        <v>44.15</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>34</v>
+        <v>30.46</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>13.09</v>
+        <v>-0.23</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>60.58</v>
+        <v>62.12</v>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-31.66</v>
+        <v>-31.53</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>14.96</v>
+        <v>14.39</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>58.23</v>
+        <v>56.11</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>-31.76</v>
+        <v>-30.49</v>
       </c>
       <c r="P14" s="26" t="n">
-        <v>16.37</v>
+        <v>19.69</v>
       </c>
       <c r="Q14" s="26" t="n">
-        <v>60.81</v>
+        <v>64.53</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>-28.33</v>
+        <v>-20.77</v>
       </c>
       <c r="S14" s="26" t="n">
-        <v>14.38</v>
+        <v>11.14</v>
       </c>
       <c r="T14" s="26" t="n">
-        <v>41.7</v>
+        <v>42.31</v>
       </c>
       <c r="U14" s="26" t="n">
-        <v>-6.54</v>
+        <v>-9.07</v>
       </c>
       <c r="V14" s="26" t="n">
-        <v>-31.15</v>
+        <v>-27.89</v>
       </c>
       <c r="W14" s="26" t="n">
-        <v>41.41</v>
+        <v>43.24</v>
       </c>
       <c r="X14" s="26" t="n">
-        <v>-4.51</v>
+        <v>-3.65</v>
       </c>
       <c r="Y14" s="26" t="n">
-        <v>-33.64</v>
+        <v>-34.71</v>
       </c>
       <c r="Z14" s="26" t="n">
-        <v>41.99</v>
+        <v>44.79</v>
       </c>
       <c r="AA14" s="26" t="n">
-        <v>-5.43</v>
+        <v>-5.4</v>
       </c>
       <c r="AB14" s="26" t="n">
-        <v>-34.52</v>
+        <v>-39.18</v>
       </c>
       <c r="AC14" s="26" t="n">
-        <v>49.37</v>
+        <v>49.71</v>
       </c>
       <c r="AD14" s="26" t="n">
-        <v>29.97</v>
+        <v>17.52</v>
       </c>
       <c r="AE14" s="26" t="n">
-        <v>14.81</v>
+        <v>-0.31</v>
       </c>
       <c r="AF14" s="26" t="n">
-        <v>50.48</v>
+        <v>48.03</v>
       </c>
       <c r="AG14" s="26" t="n">
-        <v>33.02</v>
+        <v>29.46</v>
       </c>
       <c r="AH14" s="26" t="n">
-        <v>18.79</v>
+        <v>13.94</v>
       </c>
       <c r="AI14" s="26" t="n">
-        <v>61.94</v>
+        <v>66.27</v>
       </c>
       <c r="AJ14" s="26" t="n">
-        <v>-29.92</v>
+        <v>-25.38</v>
       </c>
       <c r="AK14" s="26" t="n">
-        <v>12.11</v>
+        <v>4.74</v>
       </c>
       <c r="AL14" s="26" t="n">
-        <v>63.12</v>
+        <v>63.69</v>
       </c>
       <c r="AM14" s="26" t="n">
-        <v>-30.6</v>
+        <v>-30.88</v>
       </c>
       <c r="AN14" s="26" t="n">
-        <v>13.85</v>
+        <v>13.74</v>
       </c>
       <c r="AO14" s="26" t="n">
-        <v>39.52</v>
+        <v>36.17</v>
       </c>
       <c r="AP14" s="26" t="n">
-        <v>-7.69</v>
+        <v>-14.94</v>
       </c>
       <c r="AQ14" s="26" t="n">
-        <v>-27.4</v>
+        <v>-24.25</v>
       </c>
       <c r="AR14" s="26" t="n">
-        <v>41.6</v>
+        <v>46.71</v>
       </c>
       <c r="AS14" s="26" t="n">
-        <v>-7.05</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="AT14" s="26" t="n">
-        <v>-28.54</v>
+        <v>-29.13</v>
       </c>
     </row>
     <row r="15">
@@ -14556,139 +14556,139 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>45.99</v>
+        <v>43.01</v>
       </c>
       <c r="C15" s="26" t="n">
-        <v>33.21</v>
+        <v>28.45</v>
       </c>
       <c r="D15" s="26" t="n">
-        <v>15.77</v>
+        <v>9.75</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>45.07</v>
+        <v>42.28</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>33.35</v>
+        <v>27.86</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>14.52</v>
+        <v>5.41</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>46.67</v>
+        <v>43.63</v>
       </c>
       <c r="I15" s="26" t="n">
-        <v>32.92</v>
+        <v>27.2</v>
       </c>
       <c r="J15" s="26" t="n">
-        <v>15.46</v>
+        <v>6.96</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>60.75</v>
+        <v>62.64</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-31.52</v>
+        <v>-31.08</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>15.15</v>
+        <v>14.96</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>57.22</v>
+        <v>53.07</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>-32.22</v>
+        <v>-31.91</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>16.6</v>
+        <v>20.39</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>59.99</v>
+        <v>62.05</v>
       </c>
       <c r="R15" s="26" t="n">
+        <v>-23.68</v>
+      </c>
+      <c r="S15" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T15" s="26" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="U15" s="26" t="n">
+        <v>-11.07</v>
+      </c>
+      <c r="V15" s="26" t="n">
+        <v>-31.79</v>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="Y15" s="26" t="n">
+        <v>-33.74</v>
+      </c>
+      <c r="Z15" s="26" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="AA15" s="26" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AB15" s="26" t="n">
+        <v>-32.78</v>
+      </c>
+      <c r="AC15" s="26" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="AD15" s="26" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AE15" s="26" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AF15" s="26" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="AG15" s="26" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="AH15" s="26" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AI15" s="26" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>63.56</v>
+      </c>
+      <c r="AM15" s="26" t="n">
+        <v>-30.37</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="AO15" s="26" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="AP15" s="26" t="n">
+        <v>-17.48</v>
+      </c>
+      <c r="AQ15" s="26" t="n">
+        <v>-19.41</v>
+      </c>
+      <c r="AR15" s="26" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="AS15" s="26" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="AT15" s="26" t="n">
         <v>-29.29</v>
-      </c>
-      <c r="S15" s="26" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="T15" s="26" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="U15" s="26" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="V15" s="26" t="n">
-        <v>-32.43</v>
-      </c>
-      <c r="W15" s="26" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="X15" s="26" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="Y15" s="26" t="n">
-        <v>-33.32</v>
-      </c>
-      <c r="Z15" s="26" t="n">
-        <v>41.96</v>
-      </c>
-      <c r="AA15" s="26" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="AB15" s="26" t="n">
-        <v>-32.41</v>
-      </c>
-      <c r="AC15" s="26" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="AD15" s="26" t="n">
-        <v>29.19</v>
-      </c>
-      <c r="AE15" s="26" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="AF15" s="26" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="AG15" s="26" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="AH15" s="26" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="AI15" s="26" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="AJ15" s="26" t="n">
-        <v>-28.08</v>
-      </c>
-      <c r="AK15" s="26" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>63.08</v>
-      </c>
-      <c r="AM15" s="26" t="n">
-        <v>-30.44</v>
-      </c>
-      <c r="AN15" s="26" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="AO15" s="26" t="n">
-        <v>40.05</v>
-      </c>
-      <c r="AP15" s="26" t="n">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="AQ15" s="26" t="n">
-        <v>-25.8</v>
-      </c>
-      <c r="AR15" s="26" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="AS15" s="26" t="n">
-        <v>-7.72</v>
-      </c>
-      <c r="AT15" s="26" t="n">
-        <v>-28.59</v>
       </c>
     </row>
     <row r="16">
@@ -14698,139 +14698,139 @@
         </is>
       </c>
       <c r="B16" s="26" t="n">
-        <v>47.02</v>
+        <v>46.14</v>
       </c>
       <c r="C16" s="26" t="n">
-        <v>33.11</v>
+        <v>28.13</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>15.42</v>
+        <v>8.69</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>45.32</v>
+        <v>43.01</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>33.39</v>
+        <v>27.97</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>14.89</v>
+        <v>6.54</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>45.91</v>
+        <v>41.33</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>33.46</v>
+        <v>28.83</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>14.72</v>
+        <v>4.72</v>
       </c>
       <c r="K16" s="26" t="n">
-        <v>61.32</v>
+        <v>64.36</v>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-31</v>
+        <v>-29.51</v>
       </c>
       <c r="M16" s="26" t="n">
-        <v>14.99</v>
+        <v>14.49</v>
       </c>
       <c r="N16" s="26" t="n">
-        <v>58.61</v>
+        <v>57.28</v>
       </c>
       <c r="O16" s="26" t="n">
-        <v>-31.5</v>
+        <v>-29.7</v>
       </c>
       <c r="P16" s="26" t="n">
-        <v>16.71</v>
+        <v>20.71</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>61</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>-28.36</v>
+        <v>-20.87</v>
       </c>
       <c r="S16" s="26" t="n">
-        <v>14.26</v>
+        <v>10.75</v>
       </c>
       <c r="T16" s="26" t="n">
-        <v>44.63</v>
+        <v>51.19</v>
       </c>
       <c r="U16" s="26" t="n">
-        <v>-7.07</v>
+        <v>-10.66</v>
       </c>
       <c r="V16" s="26" t="n">
-        <v>-30.34</v>
+        <v>-25.43</v>
       </c>
       <c r="W16" s="26" t="n">
-        <v>41.08</v>
+        <v>42.25</v>
       </c>
       <c r="X16" s="26" t="n">
-        <v>-4.73</v>
+        <v>-4.3</v>
       </c>
       <c r="Y16" s="26" t="n">
-        <v>-33.4</v>
+        <v>-34</v>
       </c>
       <c r="Z16" s="26" t="n">
-        <v>42.28</v>
+        <v>45.67</v>
       </c>
       <c r="AA16" s="26" t="n">
-        <v>-4.09</v>
+        <v>-1.35</v>
       </c>
       <c r="AB16" s="26" t="n">
-        <v>-32.09</v>
+        <v>-31.82</v>
       </c>
       <c r="AC16" s="26" t="n">
-        <v>49.6</v>
+        <v>50.4</v>
       </c>
       <c r="AD16" s="26" t="n">
-        <v>28.14</v>
+        <v>11.95</v>
       </c>
       <c r="AE16" s="26" t="n">
-        <v>16.51</v>
+        <v>4.86</v>
       </c>
       <c r="AF16" s="26" t="n">
-        <v>50.75</v>
+        <v>48.87</v>
       </c>
       <c r="AG16" s="26" t="n">
-        <v>32.42</v>
+        <v>27.64</v>
       </c>
       <c r="AH16" s="26" t="n">
-        <v>19.03</v>
+        <v>14.67</v>
       </c>
       <c r="AI16" s="26" t="n">
-        <v>63.39</v>
+        <v>70.67</v>
       </c>
       <c r="AJ16" s="26" t="n">
-        <v>-28.63</v>
+        <v>-21.45</v>
       </c>
       <c r="AK16" s="26" t="n">
-        <v>11.42</v>
+        <v>2.66</v>
       </c>
       <c r="AL16" s="26" t="n">
-        <v>63.01</v>
+        <v>63.34</v>
       </c>
       <c r="AM16" s="26" t="n">
-        <v>-30.29</v>
+        <v>-29.92</v>
       </c>
       <c r="AN16" s="26" t="n">
-        <v>14.48</v>
+        <v>15.65</v>
       </c>
       <c r="AO16" s="26" t="n">
-        <v>39.92</v>
+        <v>37.39</v>
       </c>
       <c r="AP16" s="26" t="n">
-        <v>-6.8</v>
+        <v>-12.26</v>
       </c>
       <c r="AQ16" s="26" t="n">
-        <v>-24.59</v>
+        <v>-15.74</v>
       </c>
       <c r="AR16" s="26" t="n">
-        <v>38.52</v>
+        <v>37.38</v>
       </c>
       <c r="AS16" s="26" t="n">
-        <v>-7.33</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AT16" s="26" t="n">
-        <v>-30.36</v>
+        <v>-34.65</v>
       </c>
     </row>
     <row r="17">
@@ -14840,139 +14840,139 @@
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>46.55</v>
+        <v>44.71</v>
       </c>
       <c r="C17" s="26" t="n">
-        <v>32.74</v>
+        <v>27.02</v>
       </c>
       <c r="D17" s="26" t="n">
-        <v>15.27</v>
+        <v>8.25</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>44.82</v>
+        <v>41.51</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>34.05</v>
+        <v>29.99</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>13.64</v>
+        <v>2.76</v>
       </c>
       <c r="H17" s="26" t="n">
-        <v>46.64</v>
+        <v>43.56</v>
       </c>
       <c r="I17" s="26" t="n">
-        <v>32.89</v>
+        <v>27.09</v>
       </c>
       <c r="J17" s="26" t="n">
-        <v>14.1</v>
+        <v>2.82</v>
       </c>
       <c r="K17" s="26" t="n">
-        <v>61.23</v>
+        <v>64.11</v>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-31.92</v>
+        <v>-32.3</v>
       </c>
       <c r="M17" s="26" t="n">
-        <v>14.76</v>
+        <v>13.78</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>57.83</v>
+        <v>54.92</v>
       </c>
       <c r="O17" s="26" t="n">
-        <v>-31.09</v>
+        <v>-28.47</v>
       </c>
       <c r="P17" s="26" t="n">
-        <v>16.01</v>
+        <v>18.6</v>
       </c>
       <c r="Q17" s="26" t="n">
-        <v>60.19</v>
+        <v>62.64</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>-27.18</v>
+        <v>-17.3</v>
       </c>
       <c r="S17" s="26" t="n">
-        <v>15.15</v>
+        <v>13.47</v>
       </c>
       <c r="T17" s="26" t="n">
-        <v>45.32</v>
+        <v>53.29</v>
       </c>
       <c r="U17" s="26" t="n">
-        <v>-7.99</v>
+        <v>-13.46</v>
       </c>
       <c r="V17" s="26" t="n">
-        <v>-28.23</v>
+        <v>-19.05</v>
       </c>
       <c r="W17" s="26" t="n">
-        <v>40.97</v>
+        <v>41.91</v>
       </c>
       <c r="X17" s="26" t="n">
-        <v>-3.83</v>
+        <v>-1.59</v>
       </c>
       <c r="Y17" s="26" t="n">
-        <v>-33.71</v>
+        <v>-34.94</v>
       </c>
       <c r="Z17" s="26" t="n">
-        <v>42.21</v>
+        <v>45.45</v>
       </c>
       <c r="AA17" s="26" t="n">
-        <v>-4.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AB17" s="26" t="n">
-        <v>-30.85</v>
+        <v>-28.06</v>
       </c>
       <c r="AC17" s="26" t="n">
-        <v>50.26</v>
+        <v>52.42</v>
       </c>
       <c r="AD17" s="26" t="n">
-        <v>28.54</v>
+        <v>13.18</v>
       </c>
       <c r="AE17" s="26" t="n">
-        <v>16.68</v>
+        <v>5.36</v>
       </c>
       <c r="AF17" s="26" t="n">
-        <v>50.62</v>
+        <v>48.46</v>
       </c>
       <c r="AG17" s="26" t="n">
-        <v>31.88</v>
+        <v>26</v>
       </c>
       <c r="AH17" s="26" t="n">
-        <v>17.17</v>
+        <v>9.02</v>
       </c>
       <c r="AI17" s="26" t="n">
-        <v>61.92</v>
+        <v>66.22</v>
       </c>
       <c r="AJ17" s="26" t="n">
-        <v>-28.93</v>
+        <v>-22.36</v>
       </c>
       <c r="AK17" s="26" t="n">
-        <v>10.58</v>
+        <v>0.11</v>
       </c>
       <c r="AL17" s="26" t="n">
-        <v>63.11</v>
+        <v>63.65</v>
       </c>
       <c r="AM17" s="26" t="n">
-        <v>-30.3</v>
+        <v>-29.96</v>
       </c>
       <c r="AN17" s="26" t="n">
-        <v>14.74</v>
+        <v>16.45</v>
       </c>
       <c r="AO17" s="26" t="n">
-        <v>37.8</v>
+        <v>30.96</v>
       </c>
       <c r="AP17" s="26" t="n">
-        <v>-6.02</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AQ17" s="26" t="n">
-        <v>-26.81</v>
+        <v>-22.45</v>
       </c>
       <c r="AR17" s="26" t="n">
-        <v>40.82</v>
+        <v>44.37</v>
       </c>
       <c r="AS17" s="26" t="n">
-        <v>-7.34</v>
+        <v>-9.99</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-30.27</v>
+        <v>-34.36</v>
       </c>
     </row>
     <row r="18">
@@ -14982,139 +14982,139 @@
         </is>
       </c>
       <c r="B18" s="26" t="n">
-        <v>45.69</v>
+        <v>42.12</v>
       </c>
       <c r="C18" s="26" t="n">
-        <v>32.9</v>
+        <v>27.49</v>
       </c>
       <c r="D18" s="26" t="n">
-        <v>14.77</v>
+        <v>6.72</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>44.47</v>
+        <v>40.46</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>33.13</v>
+        <v>27.19</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>14.49</v>
+        <v>5.34</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>46.38</v>
+        <v>42.77</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>32.81</v>
+        <v>26.85</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>14.77</v>
+        <v>4.86</v>
       </c>
       <c r="K18" s="26" t="n">
-        <v>61.19</v>
+        <v>63.98</v>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-31.95</v>
+        <v>-32.39</v>
       </c>
       <c r="M18" s="26" t="n">
-        <v>14.94</v>
+        <v>14.34</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>58.48</v>
+        <v>56.86</v>
       </c>
       <c r="O18" s="26" t="n">
-        <v>-31.26</v>
+        <v>-28.99</v>
       </c>
       <c r="P18" s="26" t="n">
-        <v>17.58</v>
+        <v>23.34</v>
       </c>
       <c r="Q18" s="26" t="n">
-        <v>60</v>
+        <v>62.08</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>-28.52</v>
+        <v>-21.33</v>
       </c>
       <c r="S18" s="26" t="n">
-        <v>13.97</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="T18" s="26" t="n">
-        <v>46.09</v>
+        <v>55.63</v>
       </c>
       <c r="U18" s="26" t="n">
-        <v>-7.12</v>
+        <v>-10.81</v>
       </c>
       <c r="V18" s="26" t="n">
-        <v>-31.83</v>
+        <v>-29.96</v>
       </c>
       <c r="W18" s="26" t="n">
-        <v>41.55</v>
+        <v>43.65</v>
       </c>
       <c r="X18" s="26" t="n">
-        <v>-3.63</v>
+        <v>-0.98</v>
       </c>
       <c r="Y18" s="26" t="n">
-        <v>-33.98</v>
+        <v>-35.75</v>
       </c>
       <c r="Z18" s="26" t="n">
-        <v>42.18</v>
+        <v>45.36</v>
       </c>
       <c r="AA18" s="26" t="n">
-        <v>-4.41</v>
+        <v>-2.32</v>
       </c>
       <c r="AB18" s="26" t="n">
-        <v>-32.31</v>
+        <v>-32.48</v>
       </c>
       <c r="AC18" s="26" t="n">
-        <v>51.28</v>
+        <v>55.52</v>
       </c>
       <c r="AD18" s="26" t="n">
-        <v>29.07</v>
+        <v>14.78</v>
       </c>
       <c r="AE18" s="26" t="n">
-        <v>12.64</v>
+        <v>-6.89</v>
       </c>
       <c r="AF18" s="26" t="n">
-        <v>50.91</v>
+        <v>49.35</v>
       </c>
       <c r="AG18" s="26" t="n">
-        <v>32.21</v>
+        <v>27.01</v>
       </c>
       <c r="AH18" s="26" t="n">
-        <v>18.77</v>
+        <v>13.86</v>
       </c>
       <c r="AI18" s="26" t="n">
-        <v>62.13</v>
+        <v>66.84</v>
       </c>
       <c r="AJ18" s="26" t="n">
-        <v>-27.58</v>
+        <v>-18.29</v>
       </c>
       <c r="AK18" s="26" t="n">
-        <v>11.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL18" s="26" t="n">
-        <v>63.09</v>
+        <v>63.59</v>
       </c>
       <c r="AM18" s="26" t="n">
-        <v>-30.22</v>
+        <v>-29.72</v>
       </c>
       <c r="AN18" s="26" t="n">
-        <v>13.99</v>
+        <v>14.17</v>
       </c>
       <c r="AO18" s="26" t="n">
-        <v>38.81</v>
+        <v>34.02</v>
       </c>
       <c r="AP18" s="26" t="n">
-        <v>-8.15</v>
+        <v>-16.35</v>
       </c>
       <c r="AQ18" s="26" t="n">
-        <v>-28.98</v>
+        <v>-29.02</v>
       </c>
       <c r="AR18" s="26" t="n">
-        <v>40.64</v>
+        <v>43.82</v>
       </c>
       <c r="AS18" s="26" t="n">
-        <v>-7.15</v>
+        <v>-9.4</v>
       </c>
       <c r="AT18" s="26" t="n">
-        <v>-31.6</v>
+        <v>-38.4</v>
       </c>
     </row>
     <row r="19">
@@ -15124,139 +15124,139 @@
         </is>
       </c>
       <c r="B19" s="26" t="n">
-        <v>46.46</v>
+        <v>44.46</v>
       </c>
       <c r="C19" s="26" t="n">
-        <v>31.03</v>
+        <v>21.83</v>
       </c>
       <c r="D19" s="26" t="n">
-        <v>14.71</v>
+        <v>6.55</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>44.47</v>
+        <v>40.45</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>32.89</v>
+        <v>26.46</v>
       </c>
       <c r="G19" s="26" t="n">
-        <v>14.06</v>
+        <v>4.03</v>
       </c>
       <c r="H19" s="26" t="n">
-        <v>46.37</v>
+        <v>42.72</v>
       </c>
       <c r="I19" s="26" t="n">
-        <v>32.74</v>
+        <v>26.64</v>
       </c>
       <c r="J19" s="26" t="n">
-        <v>12.09</v>
+        <v>-3.27</v>
       </c>
       <c r="K19" s="26" t="n">
-        <v>60.52</v>
+        <v>61.95</v>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-31.64</v>
+        <v>-31.47</v>
       </c>
       <c r="M19" s="26" t="n">
-        <v>15.04</v>
+        <v>14.65</v>
       </c>
       <c r="N19" s="26" t="n">
-        <v>57.27</v>
+        <v>53.22</v>
       </c>
       <c r="O19" s="26" t="n">
-        <v>-31.95</v>
+        <v>-31.07</v>
       </c>
       <c r="P19" s="26" t="n">
-        <v>16.99</v>
+        <v>21.56</v>
       </c>
       <c r="Q19" s="26" t="n">
-        <v>59.61</v>
+        <v>60.88</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>-28.73</v>
+        <v>-22</v>
       </c>
       <c r="S19" s="26" t="n">
-        <v>13.22</v>
+        <v>7.6</v>
       </c>
       <c r="T19" s="26" t="n">
-        <v>45.7</v>
+        <v>54.43</v>
       </c>
       <c r="U19" s="26" t="n">
-        <v>-8.130000000000001</v>
+        <v>-13.88</v>
       </c>
       <c r="V19" s="26" t="n">
-        <v>-30.91</v>
+        <v>-27.16</v>
       </c>
       <c r="W19" s="26" t="n">
-        <v>41.12</v>
+        <v>42.35</v>
       </c>
       <c r="X19" s="26" t="n">
-        <v>-4.59</v>
+        <v>-3.9</v>
       </c>
       <c r="Y19" s="26" t="n">
-        <v>-33.84</v>
+        <v>-35.32</v>
       </c>
       <c r="Z19" s="26" t="n">
-        <v>42.85</v>
+        <v>47.4</v>
       </c>
       <c r="AA19" s="26" t="n">
-        <v>-4.75</v>
+        <v>-3.33</v>
       </c>
       <c r="AB19" s="26" t="n">
-        <v>-30.54</v>
+        <v>-27.14</v>
       </c>
       <c r="AC19" s="26" t="n">
-        <v>50.71</v>
+        <v>53.78</v>
       </c>
       <c r="AD19" s="26" t="n">
-        <v>26.38</v>
+        <v>6.63</v>
       </c>
       <c r="AE19" s="26" t="n">
-        <v>13.6</v>
+        <v>-3.98</v>
       </c>
       <c r="AF19" s="26" t="n">
-        <v>51.07</v>
+        <v>49.82</v>
       </c>
       <c r="AG19" s="26" t="n">
-        <v>31.68</v>
+        <v>25.41</v>
       </c>
       <c r="AH19" s="26" t="n">
-        <v>17.89</v>
+        <v>11.19</v>
       </c>
       <c r="AI19" s="26" t="n">
-        <v>62.76</v>
+        <v>68.75</v>
       </c>
       <c r="AJ19" s="26" t="n">
-        <v>-26.98</v>
+        <v>-16.47</v>
       </c>
       <c r="AK19" s="26" t="n">
-        <v>10.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AL19" s="26" t="n">
-        <v>63.15</v>
+        <v>63.77</v>
       </c>
       <c r="AM19" s="26" t="n">
-        <v>-30.32</v>
+        <v>-30.03</v>
       </c>
       <c r="AN19" s="26" t="n">
-        <v>14.23</v>
+        <v>14.91</v>
       </c>
       <c r="AO19" s="26" t="n">
-        <v>39.68</v>
+        <v>36.67</v>
       </c>
       <c r="AP19" s="26" t="n">
-        <v>-8.960000000000001</v>
+        <v>-18.81</v>
       </c>
       <c r="AQ19" s="26" t="n">
-        <v>-26.32</v>
+        <v>-20.98</v>
       </c>
       <c r="AR19" s="26" t="n">
-        <v>41.23</v>
+        <v>45.61</v>
       </c>
       <c r="AS19" s="26" t="n">
-        <v>-8.130000000000001</v>
+        <v>-12.37</v>
       </c>
       <c r="AT19" s="26" t="n">
-        <v>-30.21</v>
+        <v>-34.21</v>
       </c>
     </row>
     <row r="20">
@@ -15266,139 +15266,139 @@
         </is>
       </c>
       <c r="B20" s="26" t="n">
-        <v>45.35</v>
+        <v>41.1</v>
       </c>
       <c r="C20" s="26" t="n">
-        <v>32.15</v>
+        <v>25.23</v>
       </c>
       <c r="D20" s="26" t="n">
-        <v>14.5</v>
+        <v>5.91</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>44.07</v>
+        <v>39.25</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>32.62</v>
+        <v>25.65</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>13.36</v>
+        <v>1.89</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>47.25</v>
+        <v>45.4</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>32.67</v>
+        <v>26.44</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>14.33</v>
+        <v>3.51</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>60.96</v>
+        <v>63.27</v>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-31.05</v>
+        <v>-29.68</v>
       </c>
       <c r="M20" s="26" t="n">
-        <v>14.26</v>
+        <v>12.28</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>58.46</v>
+        <v>56.82</v>
       </c>
       <c r="O20" s="26" t="n">
-        <v>-31.42</v>
+        <v>-29.46</v>
       </c>
       <c r="P20" s="26" t="n">
-        <v>17.26</v>
+        <v>22.37</v>
       </c>
       <c r="Q20" s="26" t="n">
-        <v>59.09</v>
+        <v>59.31</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>-28.63</v>
+        <v>-21.68</v>
       </c>
       <c r="S20" s="26" t="n">
-        <v>11.07</v>
+        <v>1.11</v>
       </c>
       <c r="T20" s="26" t="n">
-        <v>45.8</v>
+        <v>54.74</v>
       </c>
       <c r="U20" s="26" t="n">
-        <v>-7.25</v>
+        <v>-11.2</v>
       </c>
       <c r="V20" s="26" t="n">
-        <v>-29.84</v>
+        <v>-23.92</v>
       </c>
       <c r="W20" s="26" t="n">
-        <v>41.77</v>
+        <v>44.32</v>
       </c>
       <c r="X20" s="26" t="n">
-        <v>-4.3</v>
+        <v>-3.01</v>
       </c>
       <c r="Y20" s="26" t="n">
-        <v>-35.43</v>
+        <v>-40.14</v>
       </c>
       <c r="Z20" s="26" t="n">
-        <v>42.64</v>
+        <v>46.78</v>
       </c>
       <c r="AA20" s="26" t="n">
-        <v>-5.36</v>
+        <v>-5.19</v>
       </c>
       <c r="AB20" s="26" t="n">
-        <v>-28.2</v>
+        <v>-20.02</v>
       </c>
       <c r="AC20" s="26" t="n">
-        <v>50.67</v>
+        <v>53.67</v>
       </c>
       <c r="AD20" s="26" t="n">
-        <v>26.73</v>
+        <v>7.7</v>
       </c>
       <c r="AE20" s="26" t="n">
-        <v>11.56</v>
+        <v>-10.15</v>
       </c>
       <c r="AF20" s="26" t="n">
-        <v>51.1</v>
+        <v>49.91</v>
       </c>
       <c r="AG20" s="26" t="n">
-        <v>31.39</v>
+        <v>24.53</v>
       </c>
       <c r="AH20" s="26" t="n">
-        <v>17.9</v>
+        <v>11.22</v>
       </c>
       <c r="AI20" s="26" t="n">
-        <v>63.22</v>
+        <v>70.14</v>
       </c>
       <c r="AJ20" s="26" t="n">
-        <v>-27.15</v>
+        <v>-16.97</v>
       </c>
       <c r="AK20" s="26" t="n">
-        <v>10.05</v>
+        <v>-1.5</v>
       </c>
       <c r="AL20" s="26" t="n">
-        <v>63.15</v>
+        <v>63.77</v>
       </c>
       <c r="AM20" s="26" t="n">
-        <v>-29.98</v>
+        <v>-29</v>
       </c>
       <c r="AN20" s="26" t="n">
-        <v>14.31</v>
+        <v>15.15</v>
       </c>
       <c r="AO20" s="26" t="n">
-        <v>40.32</v>
+        <v>38.6</v>
       </c>
       <c r="AP20" s="26" t="n">
-        <v>-7.49</v>
+        <v>-14.35</v>
       </c>
       <c r="AQ20" s="26" t="n">
-        <v>-24.5</v>
+        <v>-15.46</v>
       </c>
       <c r="AR20" s="26" t="n">
-        <v>41.2</v>
+        <v>45.49</v>
       </c>
       <c r="AS20" s="26" t="n">
-        <v>-7.16</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="AT20" s="26" t="n">
-        <v>-29.02</v>
+        <v>-30.6</v>
       </c>
     </row>
     <row r="21">
@@ -15408,139 +15408,139 @@
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>46.55</v>
+        <v>44.73</v>
       </c>
       <c r="C21" s="26" t="n">
-        <v>32.32</v>
+        <v>25.75</v>
       </c>
       <c r="D21" s="26" t="n">
-        <v>14.26</v>
+        <v>5.17</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>44.19</v>
+        <v>39.61</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>33.18</v>
+        <v>27.34</v>
       </c>
       <c r="G21" s="26" t="n">
-        <v>12.77</v>
+        <v>0.11</v>
       </c>
       <c r="H21" s="26" t="n">
-        <v>45.41</v>
+        <v>39.83</v>
       </c>
       <c r="I21" s="26" t="n">
-        <v>32.36</v>
+        <v>25.5</v>
       </c>
       <c r="J21" s="26" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="K21" s="26" t="n">
-        <v>61.45</v>
+        <v>64.77</v>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-31.96</v>
+        <v>-32.42</v>
       </c>
       <c r="M21" s="26" t="n">
-        <v>15.1</v>
+        <v>14.81</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>57.9</v>
+        <v>55.13</v>
       </c>
       <c r="O21" s="26" t="n">
-        <v>-32.04</v>
+        <v>-31.35</v>
       </c>
       <c r="P21" s="26" t="n">
-        <v>17.57</v>
+        <v>23.33</v>
       </c>
       <c r="Q21" s="26" t="n">
-        <v>60.37</v>
+        <v>63.19</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>-26.88</v>
+        <v>-16.36</v>
       </c>
       <c r="S21" s="26" t="n">
-        <v>11.21</v>
+        <v>1.52</v>
       </c>
       <c r="T21" s="26" t="n">
-        <v>45.05</v>
+        <v>52.47</v>
       </c>
       <c r="U21" s="26" t="n">
-        <v>-8.050000000000001</v>
+        <v>-13.63</v>
       </c>
       <c r="V21" s="26" t="n">
-        <v>-30.27</v>
+        <v>-25.23</v>
       </c>
       <c r="W21" s="26" t="n">
-        <v>41.4</v>
+        <v>43.21</v>
       </c>
       <c r="X21" s="26" t="n">
-        <v>-3.98</v>
+        <v>-2.04</v>
       </c>
       <c r="Y21" s="26" t="n">
-        <v>-33.97</v>
+        <v>-35.7</v>
       </c>
       <c r="Z21" s="26" t="n">
-        <v>42.69</v>
+        <v>46.91</v>
       </c>
       <c r="AA21" s="26" t="n">
-        <v>-4.95</v>
+        <v>-3.94</v>
       </c>
       <c r="AB21" s="26" t="n">
-        <v>-29.79</v>
+        <v>-24.86</v>
       </c>
       <c r="AC21" s="26" t="n">
-        <v>51.16</v>
+        <v>55.14</v>
       </c>
       <c r="AD21" s="26" t="n">
-        <v>26.52</v>
+        <v>7.06</v>
       </c>
       <c r="AE21" s="26" t="n">
-        <v>11.73</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="AF21" s="26" t="n">
-        <v>50.25</v>
+        <v>47.34</v>
       </c>
       <c r="AG21" s="26" t="n">
-        <v>31.93</v>
+        <v>26.17</v>
       </c>
       <c r="AH21" s="26" t="n">
-        <v>17.78</v>
+        <v>10.89</v>
       </c>
       <c r="AI21" s="26" t="n">
-        <v>62.8</v>
+        <v>68.88</v>
       </c>
       <c r="AJ21" s="26" t="n">
-        <v>-27.03</v>
+        <v>-16.61</v>
       </c>
       <c r="AK21" s="26" t="n">
-        <v>9.09</v>
+        <v>-4.41</v>
       </c>
       <c r="AL21" s="26" t="n">
-        <v>63.2</v>
+        <v>63.92</v>
       </c>
       <c r="AM21" s="26" t="n">
-        <v>-30.33</v>
+        <v>-30.04</v>
       </c>
       <c r="AN21" s="26" t="n">
-        <v>13.93</v>
+        <v>13.98</v>
       </c>
       <c r="AO21" s="26" t="n">
-        <v>37.45</v>
+        <v>29.89</v>
       </c>
       <c r="AP21" s="26" t="n">
-        <v>-7.58</v>
+        <v>-14.6</v>
       </c>
       <c r="AQ21" s="26" t="n">
-        <v>-24.86</v>
+        <v>-16.54</v>
       </c>
       <c r="AR21" s="26" t="n">
-        <v>41.85</v>
+        <v>47.48</v>
       </c>
       <c r="AS21" s="26" t="n">
-        <v>-8.890000000000001</v>
+        <v>-14.67</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-29.45</v>
+        <v>-31.87</v>
       </c>
     </row>
     <row r="22">
@@ -15550,139 +15550,139 @@
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>46.65</v>
+        <v>45.04</v>
       </c>
       <c r="C22" s="26" t="n">
-        <v>31.41</v>
+        <v>22.98</v>
       </c>
       <c r="D22" s="26" t="n">
-        <v>14.01</v>
+        <v>4.41</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>43.94</v>
+        <v>38.83</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>32.83</v>
+        <v>26.28</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>12.48</v>
+        <v>-0.77</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>46.41</v>
+        <v>42.86</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>32.37</v>
+        <v>25.54</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>11.78</v>
+        <v>-4.22</v>
       </c>
       <c r="K22" s="26" t="n">
-        <v>61.69</v>
+        <v>65.48</v>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-32.41</v>
+        <v>-33.8</v>
       </c>
       <c r="M22" s="26" t="n">
-        <v>14.66</v>
+        <v>13.49</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>57.74</v>
+        <v>54.64</v>
       </c>
       <c r="O22" s="26" t="n">
-        <v>-31.18</v>
+        <v>-28.75</v>
       </c>
       <c r="P22" s="26" t="n">
-        <v>16.75</v>
+        <v>20.83</v>
       </c>
       <c r="Q22" s="26" t="n">
-        <v>60.9</v>
+        <v>64.81</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>-28.04</v>
+        <v>-19.89</v>
       </c>
       <c r="S22" s="26" t="n">
-        <v>14.49</v>
+        <v>11.48</v>
       </c>
       <c r="T22" s="26" t="n">
-        <v>45.56</v>
+        <v>54.01</v>
       </c>
       <c r="U22" s="26" t="n">
-        <v>-8.18</v>
+        <v>-14.03</v>
       </c>
       <c r="V22" s="26" t="n">
-        <v>-31.25</v>
+        <v>-28.2</v>
       </c>
       <c r="W22" s="26" t="n">
-        <v>41.89</v>
+        <v>44.69</v>
       </c>
       <c r="X22" s="26" t="n">
-        <v>-4.1</v>
+        <v>-2.39</v>
       </c>
       <c r="Y22" s="26" t="n">
-        <v>-34.36</v>
+        <v>-36.91</v>
       </c>
       <c r="Z22" s="26" t="n">
-        <v>42.37</v>
+        <v>45.96</v>
       </c>
       <c r="AA22" s="26" t="n">
-        <v>-4.7</v>
+        <v>-3.18</v>
       </c>
       <c r="AB22" s="26" t="n">
-        <v>-30.99</v>
+        <v>-28.49</v>
       </c>
       <c r="AC22" s="26" t="n">
-        <v>52.07</v>
+        <v>57.9</v>
       </c>
       <c r="AD22" s="26" t="n">
-        <v>25.73</v>
+        <v>4.65</v>
       </c>
       <c r="AE22" s="26" t="n">
-        <v>10.99</v>
+        <v>-11.89</v>
       </c>
       <c r="AF22" s="26" t="n">
-        <v>50.61</v>
+        <v>48.42</v>
       </c>
       <c r="AG22" s="26" t="n">
-        <v>31.77</v>
+        <v>25.67</v>
       </c>
       <c r="AH22" s="26" t="n">
-        <v>17.48</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI22" s="26" t="n">
-        <v>64.23999999999999</v>
+        <v>73.22</v>
       </c>
       <c r="AJ22" s="26" t="n">
-        <v>-26.6</v>
+        <v>-15.31</v>
       </c>
       <c r="AK22" s="26" t="n">
-        <v>10.14</v>
+        <v>-1.21</v>
       </c>
       <c r="AL22" s="26" t="n">
-        <v>63.27</v>
+        <v>64.14</v>
       </c>
       <c r="AM22" s="26" t="n">
-        <v>-30.02</v>
+        <v>-29.1</v>
       </c>
       <c r="AN22" s="26" t="n">
-        <v>14.57</v>
+        <v>15.92</v>
       </c>
       <c r="AO22" s="26" t="n">
-        <v>39.59</v>
+        <v>36.4</v>
       </c>
       <c r="AP22" s="26" t="n">
-        <v>-6.96</v>
+        <v>-12.72</v>
       </c>
       <c r="AQ22" s="26" t="n">
-        <v>-24.87</v>
+        <v>-16.59</v>
       </c>
       <c r="AR22" s="26" t="n">
-        <v>43.42</v>
+        <v>52.23</v>
       </c>
       <c r="AS22" s="26" t="n">
-        <v>-7.86</v>
+        <v>-11.57</v>
       </c>
       <c r="AT22" s="26" t="n">
-        <v>-30.08</v>
+        <v>-33.81</v>
       </c>
     </row>
     <row r="23">
@@ -15692,139 +15692,139 @@
         </is>
       </c>
       <c r="B23" s="26" t="n">
-        <v>45.98</v>
+        <v>43.01</v>
       </c>
       <c r="C23" s="26" t="n">
-        <v>32.14</v>
+        <v>25.2</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>13.79</v>
+        <v>3.76</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>44.06</v>
+        <v>39.22</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>32.79</v>
+        <v>26.18</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>13.1</v>
+        <v>1.12</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>45.73</v>
+        <v>40.79</v>
       </c>
       <c r="I23" s="26" t="n">
-        <v>32.87</v>
+        <v>27.03</v>
       </c>
       <c r="J23" s="26" t="n">
-        <v>12.75</v>
+        <v>-1.26</v>
       </c>
       <c r="K23" s="26" t="n">
-        <v>61.32</v>
+        <v>64.36</v>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-31.55</v>
+        <v>-31.19</v>
       </c>
       <c r="M23" s="26" t="n">
-        <v>14.84</v>
+        <v>14.01</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>57.54</v>
+        <v>54.01</v>
       </c>
       <c r="O23" s="26" t="n">
-        <v>-31.16</v>
+        <v>-28.69</v>
       </c>
       <c r="P23" s="26" t="n">
-        <v>17.52</v>
+        <v>23.16</v>
       </c>
       <c r="Q23" s="26" t="n">
-        <v>60.7</v>
+        <v>64.19</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>-26.89</v>
+        <v>-16.41</v>
       </c>
       <c r="S23" s="26" t="n">
-        <v>13.64</v>
+        <v>8.9</v>
       </c>
       <c r="T23" s="26" t="n">
-        <v>47.89</v>
+        <v>61.07</v>
       </c>
       <c r="U23" s="26" t="n">
-        <v>-8.5</v>
+        <v>-14.98</v>
       </c>
       <c r="V23" s="26" t="n">
-        <v>-28.58</v>
+        <v>-20.12</v>
       </c>
       <c r="W23" s="26" t="n">
-        <v>41.75</v>
+        <v>44.27</v>
       </c>
       <c r="X23" s="26" t="n">
-        <v>-3.56</v>
+        <v>-0.75</v>
       </c>
       <c r="Y23" s="26" t="n">
-        <v>-34.66</v>
+        <v>-37.81</v>
       </c>
       <c r="Z23" s="26" t="n">
-        <v>42.49</v>
+        <v>46.31</v>
       </c>
       <c r="AA23" s="26" t="n">
-        <v>-4.92</v>
+        <v>-3.86</v>
       </c>
       <c r="AB23" s="26" t="n">
-        <v>-31.06</v>
+        <v>-28.69</v>
       </c>
       <c r="AC23" s="26" t="n">
-        <v>50.93</v>
+        <v>54.46</v>
       </c>
       <c r="AD23" s="26" t="n">
-        <v>25.07</v>
+        <v>2.66</v>
       </c>
       <c r="AE23" s="26" t="n">
-        <v>12.92</v>
+        <v>-6.03</v>
       </c>
       <c r="AF23" s="26" t="n">
-        <v>51.35</v>
+        <v>50.67</v>
       </c>
       <c r="AG23" s="26" t="n">
-        <v>31.91</v>
+        <v>26.1</v>
       </c>
       <c r="AH23" s="26" t="n">
-        <v>18.54</v>
+        <v>13.16</v>
       </c>
       <c r="AI23" s="26" t="n">
-        <v>63.75</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="AJ23" s="26" t="n">
-        <v>-26.42</v>
+        <v>-14.77</v>
       </c>
       <c r="AK23" s="26" t="n">
-        <v>9.4</v>
+        <v>-3.46</v>
       </c>
       <c r="AL23" s="26" t="n">
-        <v>63.18</v>
+        <v>63.85</v>
       </c>
       <c r="AM23" s="26" t="n">
-        <v>-29.86</v>
+        <v>-28.63</v>
       </c>
       <c r="AN23" s="26" t="n">
-        <v>14.16</v>
+        <v>14.68</v>
       </c>
       <c r="AO23" s="26" t="n">
-        <v>39.92</v>
+        <v>37.39</v>
       </c>
       <c r="AP23" s="26" t="n">
-        <v>-6.6</v>
+        <v>-11.64</v>
       </c>
       <c r="AQ23" s="26" t="n">
-        <v>-25.66</v>
+        <v>-18.96</v>
       </c>
       <c r="AR23" s="26" t="n">
-        <v>42.34</v>
+        <v>48.96</v>
       </c>
       <c r="AS23" s="26" t="n">
-        <v>-7.83</v>
+        <v>-11.47</v>
       </c>
       <c r="AT23" s="26" t="n">
-        <v>-30.04</v>
+        <v>-33.67</v>
       </c>
     </row>
     <row r="24">
@@ -15834,139 +15834,139 @@
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>46.29</v>
+        <v>43.94</v>
       </c>
       <c r="C24" s="26" t="n">
-        <v>31.67</v>
+        <v>23.79</v>
       </c>
       <c r="D24" s="26" t="n">
-        <v>13.64</v>
+        <v>3.3</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>43.7</v>
+        <v>38.11</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>31.67</v>
+        <v>22.78</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>13.27</v>
+        <v>1.64</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>45.79</v>
+        <v>40.98</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>32.45</v>
+        <v>25.78</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>10.29</v>
+        <v>-8.74</v>
       </c>
       <c r="K24" s="26" t="n">
-        <v>62.95</v>
+        <v>69.3</v>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-31.18</v>
+        <v>-30.07</v>
       </c>
       <c r="M24" s="26" t="n">
-        <v>15.01</v>
+        <v>14.55</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>57.25</v>
+        <v>53.14</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>-32.07</v>
+        <v>-31.43</v>
       </c>
       <c r="P24" s="26" t="n">
-        <v>17.26</v>
+        <v>22.37</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>60.44</v>
+        <v>63.39</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>-26.14</v>
+        <v>-14.13</v>
       </c>
       <c r="S24" s="26" t="n">
-        <v>12.23</v>
+        <v>4.62</v>
       </c>
       <c r="T24" s="26" t="n">
-        <v>48.48</v>
+        <v>62.87</v>
       </c>
       <c r="U24" s="26" t="n">
-        <v>-8.550000000000001</v>
+        <v>-15.15</v>
       </c>
       <c r="V24" s="26" t="n">
-        <v>-27.01</v>
+        <v>-15.34</v>
       </c>
       <c r="W24" s="26" t="n">
-        <v>41.63</v>
+        <v>43.91</v>
       </c>
       <c r="X24" s="26" t="n">
-        <v>-3.84</v>
+        <v>-1.6</v>
       </c>
       <c r="Y24" s="26" t="n">
-        <v>-33.66</v>
+        <v>-34.78</v>
       </c>
       <c r="Z24" s="26" t="n">
-        <v>42.98</v>
+        <v>47.79</v>
       </c>
       <c r="AA24" s="26" t="n">
-        <v>-4.8</v>
+        <v>-3.49</v>
       </c>
       <c r="AB24" s="26" t="n">
-        <v>-31.19</v>
+        <v>-29.08</v>
       </c>
       <c r="AC24" s="26" t="n">
-        <v>51.35</v>
+        <v>55.73</v>
       </c>
       <c r="AD24" s="26" t="n">
-        <v>23.94</v>
+        <v>-0.75</v>
       </c>
       <c r="AE24" s="26" t="n">
-        <v>10.58</v>
+        <v>-13.13</v>
       </c>
       <c r="AF24" s="26" t="n">
-        <v>51.21</v>
+        <v>50.24</v>
       </c>
       <c r="AG24" s="26" t="n">
-        <v>31.17</v>
+        <v>23.85</v>
       </c>
       <c r="AH24" s="26" t="n">
-        <v>17.32</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AI24" s="26" t="n">
-        <v>63.64</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="AJ24" s="26" t="n">
-        <v>-26.62</v>
+        <v>-15.36</v>
       </c>
       <c r="AK24" s="26" t="n">
-        <v>8.31</v>
+        <v>-6.78</v>
       </c>
       <c r="AL24" s="26" t="n">
-        <v>63.21</v>
+        <v>63.94</v>
       </c>
       <c r="AM24" s="26" t="n">
-        <v>-29.94</v>
+        <v>-28.86</v>
       </c>
       <c r="AN24" s="26" t="n">
-        <v>14.34</v>
+        <v>15.22</v>
       </c>
       <c r="AO24" s="26" t="n">
-        <v>40.67</v>
+        <v>39.66</v>
       </c>
       <c r="AP24" s="26" t="n">
-        <v>-7.8</v>
+        <v>-15.29</v>
       </c>
       <c r="AQ24" s="26" t="n">
-        <v>-26.81</v>
+        <v>-22.46</v>
       </c>
       <c r="AR24" s="26" t="n">
-        <v>40.19</v>
+        <v>42.45</v>
       </c>
       <c r="AS24" s="26" t="n">
-        <v>-7.3</v>
+        <v>-9.85</v>
       </c>
       <c r="AT24" s="26" t="n">
-        <v>-30.63</v>
+        <v>-35.45</v>
       </c>
     </row>
     <row r="25">
@@ -15976,139 +15976,139 @@
         </is>
       </c>
       <c r="B25" s="26" t="n">
-        <v>47.09</v>
+        <v>46.36</v>
       </c>
       <c r="C25" s="26" t="n">
-        <v>32.64</v>
+        <v>26.72</v>
       </c>
       <c r="D25" s="26" t="n">
-        <v>13.46</v>
+        <v>2.76</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>43.62</v>
+        <v>37.89</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>31.59</v>
+        <v>22.53</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>11.85</v>
+        <v>-2.66</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>45.59</v>
+        <v>40.38</v>
       </c>
       <c r="I25" s="26" t="n">
-        <v>32.26</v>
+        <v>25.19</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>10.22</v>
+        <v>-8.92</v>
       </c>
       <c r="K25" s="26" t="n">
-        <v>62.72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-30.94</v>
+        <v>-29.33</v>
       </c>
       <c r="M25" s="26" t="n">
-        <v>14.28</v>
+        <v>12.34</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>57.9</v>
+        <v>55.12</v>
       </c>
       <c r="O25" s="26" t="n">
-        <v>-31.7</v>
+        <v>-30.31</v>
       </c>
       <c r="P25" s="26" t="n">
-        <v>17.85</v>
+        <v>24.17</v>
       </c>
       <c r="Q25" s="26" t="n">
-        <v>59.98</v>
+        <v>62</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>-25.98</v>
+        <v>-13.66</v>
       </c>
       <c r="S25" s="26" t="n">
-        <v>11.53</v>
+        <v>2.49</v>
       </c>
       <c r="T25" s="26" t="n">
-        <v>47.05</v>
+        <v>58.54</v>
       </c>
       <c r="U25" s="26" t="n">
-        <v>-8.130000000000001</v>
+        <v>-13.89</v>
       </c>
       <c r="V25" s="26" t="n">
-        <v>-29.43</v>
+        <v>-22.68</v>
       </c>
       <c r="W25" s="26" t="n">
-        <v>41.61</v>
+        <v>43.85</v>
       </c>
       <c r="X25" s="26" t="n">
-        <v>-2.87</v>
+        <v>1.34</v>
       </c>
       <c r="Y25" s="26" t="n">
-        <v>-35.13</v>
+        <v>-39.23</v>
       </c>
       <c r="Z25" s="26" t="n">
-        <v>43.06</v>
+        <v>48.04</v>
       </c>
       <c r="AA25" s="26" t="n">
-        <v>-4.72</v>
+        <v>-3.26</v>
       </c>
       <c r="AB25" s="26" t="n">
-        <v>-28.66</v>
+        <v>-21.43</v>
       </c>
       <c r="AC25" s="26" t="n">
-        <v>52.36</v>
+        <v>58.78</v>
       </c>
       <c r="AD25" s="26" t="n">
-        <v>24.16</v>
+        <v>-0.1</v>
       </c>
       <c r="AE25" s="26" t="n">
-        <v>11.73</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="AF25" s="26" t="n">
-        <v>50.09</v>
+        <v>46.85</v>
       </c>
       <c r="AG25" s="26" t="n">
-        <v>31.44</v>
+        <v>24.69</v>
       </c>
       <c r="AH25" s="26" t="n">
-        <v>16.3</v>
+        <v>6.4</v>
       </c>
       <c r="AI25" s="26" t="n">
-        <v>62.79</v>
+        <v>68.83</v>
       </c>
       <c r="AJ25" s="26" t="n">
-        <v>-26.03</v>
+        <v>-13.56</v>
       </c>
       <c r="AK25" s="26" t="n">
-        <v>8.92</v>
+        <v>-4.94</v>
       </c>
       <c r="AL25" s="26" t="n">
-        <v>63.2</v>
+        <v>63.92</v>
       </c>
       <c r="AM25" s="26" t="n">
-        <v>-30.01</v>
+        <v>-29.08</v>
       </c>
       <c r="AN25" s="26" t="n">
-        <v>14.26</v>
+        <v>15</v>
       </c>
       <c r="AO25" s="26" t="n">
-        <v>40.51</v>
+        <v>39.17</v>
       </c>
       <c r="AP25" s="26" t="n">
-        <v>-5.77</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="AQ25" s="26" t="n">
-        <v>-24.39</v>
+        <v>-15.12</v>
       </c>
       <c r="AR25" s="26" t="n">
-        <v>43.89</v>
+        <v>53.67</v>
       </c>
       <c r="AS25" s="26" t="n">
-        <v>-7.65</v>
+        <v>-10.91</v>
       </c>
       <c r="AT25" s="26" t="n">
-        <v>-30.07</v>
+        <v>-33.78</v>
       </c>
     </row>
     <row r="26">
@@ -16118,139 +16118,139 @@
         </is>
       </c>
       <c r="B26" s="26" t="n">
-        <v>45.99</v>
+        <v>43.01</v>
       </c>
       <c r="C26" s="26" t="n">
-        <v>32.41</v>
+        <v>26.01</v>
       </c>
       <c r="D26" s="26" t="n">
-        <v>12.93</v>
+        <v>1.14</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>43.4</v>
+        <v>37.22</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>30.68</v>
+        <v>19.76</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>12.27</v>
+        <v>-1.38</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>45.38</v>
+        <v>39.74</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>31.5</v>
+        <v>22.9</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>10.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="K26" s="26" t="n">
-        <v>62.48</v>
+        <v>67.88</v>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-31.52</v>
+        <v>-31.1</v>
       </c>
       <c r="M26" s="26" t="n">
-        <v>14.43</v>
+        <v>12.79</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>57.33</v>
+        <v>53.4</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>-31.25</v>
+        <v>-28.97</v>
       </c>
       <c r="P26" s="26" t="n">
-        <v>16.57</v>
+        <v>20.28</v>
       </c>
       <c r="Q26" s="26" t="n">
-        <v>61.44</v>
+        <v>66.42</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>-25.55</v>
+        <v>-12.35</v>
       </c>
       <c r="S26" s="26" t="n">
-        <v>8.85</v>
+        <v>-5.64</v>
       </c>
       <c r="T26" s="26" t="n">
-        <v>47.68</v>
+        <v>60.45</v>
       </c>
       <c r="U26" s="26" t="n">
-        <v>-9.65</v>
+        <v>-18.49</v>
       </c>
       <c r="V26" s="26" t="n">
-        <v>-30.62</v>
+        <v>-26.28</v>
       </c>
       <c r="W26" s="26" t="n">
-        <v>41.72</v>
+        <v>44.17</v>
       </c>
       <c r="X26" s="26" t="n">
-        <v>-3.07</v>
+        <v>0.73</v>
       </c>
       <c r="Y26" s="26" t="n">
-        <v>-35.12</v>
+        <v>-39.2</v>
       </c>
       <c r="Z26" s="26" t="n">
-        <v>43</v>
+        <v>47.86</v>
       </c>
       <c r="AA26" s="26" t="n">
-        <v>-4.69</v>
+        <v>-3.17</v>
       </c>
       <c r="AB26" s="26" t="n">
-        <v>-31.33</v>
+        <v>-29.5</v>
       </c>
       <c r="AC26" s="26" t="n">
-        <v>52.64</v>
+        <v>59.63</v>
       </c>
       <c r="AD26" s="26" t="n">
-        <v>23.13</v>
+        <v>-3.22</v>
       </c>
       <c r="AE26" s="26" t="n">
-        <v>10.71</v>
+        <v>-12.73</v>
       </c>
       <c r="AF26" s="26" t="n">
-        <v>50.95</v>
+        <v>49.48</v>
       </c>
       <c r="AG26" s="26" t="n">
-        <v>31.37</v>
+        <v>24.47</v>
       </c>
       <c r="AH26" s="26" t="n">
-        <v>16.83</v>
+        <v>7.98</v>
       </c>
       <c r="AI26" s="26" t="n">
-        <v>63.02</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AJ26" s="26" t="n">
-        <v>-25.14</v>
+        <v>-10.87</v>
       </c>
       <c r="AK26" s="26" t="n">
-        <v>7.65</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AL26" s="26" t="n">
-        <v>63.21</v>
+        <v>63.96</v>
       </c>
       <c r="AM26" s="26" t="n">
-        <v>-30.03</v>
+        <v>-29.12</v>
       </c>
       <c r="AN26" s="26" t="n">
-        <v>14.17</v>
+        <v>14.7</v>
       </c>
       <c r="AO26" s="26" t="n">
-        <v>40.4</v>
+        <v>38.83</v>
       </c>
       <c r="AP26" s="26" t="n">
-        <v>-7.66</v>
+        <v>-14.86</v>
       </c>
       <c r="AQ26" s="26" t="n">
-        <v>-25.99</v>
+        <v>-19.98</v>
       </c>
       <c r="AR26" s="26" t="n">
-        <v>44.5</v>
+        <v>55.5</v>
       </c>
       <c r="AS26" s="26" t="n">
-        <v>-8.41</v>
+        <v>-13.23</v>
       </c>
       <c r="AT26" s="26" t="n">
-        <v>-29.76</v>
+        <v>-32.84</v>
       </c>
     </row>
     <row r="27">
@@ -16260,139 +16260,139 @@
         </is>
       </c>
       <c r="B27" s="26" t="n">
-        <v>45.73</v>
+        <v>42.23</v>
       </c>
       <c r="C27" s="26" t="n">
-        <v>31.13</v>
+        <v>22.14</v>
       </c>
       <c r="D27" s="26" t="n">
-        <v>12.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>43.63</v>
+        <v>37.89</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>31.53</v>
+        <v>22.33</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>10.43</v>
+        <v>-6.97</v>
       </c>
       <c r="H27" s="26" t="n">
-        <v>45.24</v>
+        <v>39.3</v>
       </c>
       <c r="I27" s="26" t="n">
-        <v>31.16</v>
+        <v>21.87</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>9.84</v>
+        <v>-10.07</v>
       </c>
       <c r="K27" s="26" t="n">
-        <v>62.4</v>
+        <v>67.64</v>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-31.49</v>
+        <v>-31.01</v>
       </c>
       <c r="M27" s="26" t="n">
-        <v>14.51</v>
+        <v>13.03</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>56.26</v>
+        <v>50.14</v>
       </c>
       <c r="O27" s="26" t="n">
-        <v>-31.19</v>
+        <v>-28.78</v>
       </c>
       <c r="P27" s="26" t="n">
-        <v>17.58</v>
+        <v>23.35</v>
       </c>
       <c r="Q27" s="26" t="n">
-        <v>59.7</v>
+        <v>61.15</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>-25.37</v>
+        <v>-11.8</v>
       </c>
       <c r="S27" s="26" t="n">
-        <v>10.29</v>
+        <v>-1.26</v>
       </c>
       <c r="T27" s="26" t="n">
-        <v>47.01</v>
+        <v>58.43</v>
       </c>
       <c r="U27" s="26" t="n">
-        <v>-8.52</v>
+        <v>-15.07</v>
       </c>
       <c r="V27" s="26" t="n">
-        <v>-31.26</v>
+        <v>-28.23</v>
       </c>
       <c r="W27" s="26" t="n">
-        <v>41.96</v>
+        <v>44.89</v>
       </c>
       <c r="X27" s="26" t="n">
-        <v>-3.27</v>
+        <v>0.12</v>
       </c>
       <c r="Y27" s="26" t="n">
-        <v>-34.06</v>
+        <v>-35.99</v>
       </c>
       <c r="Z27" s="26" t="n">
-        <v>43.3</v>
+        <v>48.75</v>
       </c>
       <c r="AA27" s="26" t="n">
-        <v>-4.61</v>
+        <v>-2.94</v>
       </c>
       <c r="AB27" s="26" t="n">
-        <v>-30.14</v>
+        <v>-25.91</v>
       </c>
       <c r="AC27" s="26" t="n">
-        <v>52.15</v>
+        <v>58.14</v>
       </c>
       <c r="AD27" s="26" t="n">
-        <v>21.88</v>
+        <v>-7</v>
       </c>
       <c r="AE27" s="26" t="n">
-        <v>12.13</v>
+        <v>-8.43</v>
       </c>
       <c r="AF27" s="26" t="n">
-        <v>49.8</v>
+        <v>45.99</v>
       </c>
       <c r="AG27" s="26" t="n">
-        <v>31.18</v>
+        <v>23.89</v>
       </c>
       <c r="AH27" s="26" t="n">
-        <v>17.21</v>
+        <v>9.15</v>
       </c>
       <c r="AI27" s="26" t="n">
-        <v>64.26000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="AJ27" s="26" t="n">
-        <v>-24.95</v>
+        <v>-10.31</v>
       </c>
       <c r="AK27" s="26" t="n">
-        <v>7.12</v>
+        <v>-10.37</v>
       </c>
       <c r="AL27" s="26" t="n">
-        <v>63.28</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AM27" s="26" t="n">
-        <v>-29.73</v>
+        <v>-28.23</v>
       </c>
       <c r="AN27" s="26" t="n">
-        <v>14.43</v>
+        <v>15.49</v>
       </c>
       <c r="AO27" s="26" t="n">
-        <v>38.95</v>
+        <v>34.43</v>
       </c>
       <c r="AP27" s="26" t="n">
-        <v>-8.380000000000001</v>
+        <v>-17.04</v>
       </c>
       <c r="AQ27" s="26" t="n">
-        <v>-22.01</v>
+        <v>-7.9</v>
       </c>
       <c r="AR27" s="26" t="n">
-        <v>46.89</v>
+        <v>62.75</v>
       </c>
       <c r="AS27" s="26" t="n">
-        <v>-8.24</v>
+        <v>-12.7</v>
       </c>
       <c r="AT27" s="26" t="n">
-        <v>-31.6</v>
+        <v>-38.42</v>
       </c>
     </row>
     <row r="28">
@@ -16402,139 +16402,139 @@
         </is>
       </c>
       <c r="B28" s="26" t="n">
-        <v>46.84</v>
+        <v>45.61</v>
       </c>
       <c r="C28" s="26" t="n">
-        <v>31.17</v>
+        <v>22.28</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>12.36</v>
+        <v>-0.6</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>43.17</v>
+        <v>36.52</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>30.31</v>
+        <v>18.63</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>11.11</v>
+        <v>-4.93</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>45.4</v>
+        <v>39.78</v>
       </c>
       <c r="I28" s="26" t="n">
-        <v>31.88</v>
+        <v>24.04</v>
       </c>
       <c r="J28" s="26" t="n">
-        <v>9.01</v>
+        <v>-12.6</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>62.42</v>
+        <v>67.72</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-30.92</v>
+        <v>-29.28</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>14.35</v>
+        <v>12.53</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>56.62</v>
+        <v>51.23</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>-31.5</v>
+        <v>-29.72</v>
       </c>
       <c r="P28" s="26" t="n">
-        <v>17.43</v>
+        <v>22.9</v>
       </c>
       <c r="Q28" s="26" t="n">
-        <v>61.65</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>-24.48</v>
+        <v>-9.09</v>
       </c>
       <c r="S28" s="26" t="n">
-        <v>15.01</v>
+        <v>13.03</v>
       </c>
       <c r="T28" s="26" t="n">
-        <v>49.53</v>
+        <v>66.05</v>
       </c>
       <c r="U28" s="26" t="n">
-        <v>-9.02</v>
+        <v>-16.57</v>
       </c>
       <c r="V28" s="26" t="n">
-        <v>-28.95</v>
+        <v>-21.23</v>
       </c>
       <c r="W28" s="26" t="n">
-        <v>41.94</v>
+        <v>44.85</v>
       </c>
       <c r="X28" s="26" t="n">
-        <v>-2.93</v>
+        <v>1.15</v>
       </c>
       <c r="Y28" s="26" t="n">
-        <v>-35.58</v>
+        <v>-40.59</v>
       </c>
       <c r="Z28" s="26" t="n">
-        <v>43.75</v>
+        <v>50.14</v>
       </c>
       <c r="AA28" s="26" t="n">
-        <v>-5.06</v>
+        <v>-4.28</v>
       </c>
       <c r="AB28" s="26" t="n">
-        <v>-29.99</v>
+        <v>-25.46</v>
       </c>
       <c r="AC28" s="26" t="n">
-        <v>51.93</v>
+        <v>57.48</v>
       </c>
       <c r="AD28" s="26" t="n">
-        <v>23.01</v>
+        <v>-3.58</v>
       </c>
       <c r="AE28" s="26" t="n">
-        <v>7.36</v>
+        <v>-22.88</v>
       </c>
       <c r="AF28" s="26" t="n">
-        <v>50.82</v>
+        <v>49.07</v>
       </c>
       <c r="AG28" s="26" t="n">
-        <v>30.41</v>
+        <v>21.55</v>
       </c>
       <c r="AH28" s="26" t="n">
-        <v>18.01</v>
+        <v>11.58</v>
       </c>
       <c r="AI28" s="26" t="n">
-        <v>62.77</v>
+        <v>68.77</v>
       </c>
       <c r="AJ28" s="26" t="n">
-        <v>-24.74</v>
+        <v>-9.68</v>
       </c>
       <c r="AK28" s="26" t="n">
-        <v>6.79</v>
+        <v>-11.38</v>
       </c>
       <c r="AL28" s="26" t="n">
-        <v>63.46</v>
+        <v>64.72</v>
       </c>
       <c r="AM28" s="26" t="n">
-        <v>-30.09</v>
+        <v>-29.33</v>
       </c>
       <c r="AN28" s="26" t="n">
-        <v>14.37</v>
+        <v>15.31</v>
       </c>
       <c r="AO28" s="26" t="n">
-        <v>37.78</v>
+        <v>30.91</v>
       </c>
       <c r="AP28" s="26" t="n">
-        <v>-9.869999999999999</v>
+        <v>-21.54</v>
       </c>
       <c r="AQ28" s="26" t="n">
-        <v>-23.95</v>
+        <v>-13.78</v>
       </c>
       <c r="AR28" s="26" t="n">
-        <v>40.88</v>
+        <v>44.54</v>
       </c>
       <c r="AS28" s="26" t="n">
-        <v>-7.67</v>
+        <v>-10.98</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-30.3</v>
+        <v>-34.47</v>
       </c>
     </row>
     <row r="29">
@@ -16544,139 +16544,139 @@
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>47.04</v>
+        <v>46.22</v>
       </c>
       <c r="C29" s="26" t="n">
-        <v>31.09</v>
+        <v>22.01</v>
       </c>
       <c r="D29" s="26" t="n">
-        <v>12.21</v>
+        <v>-1.04</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>43.36</v>
+        <v>37.09</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>30.56</v>
+        <v>19.42</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>11.19</v>
+        <v>-4.67</v>
       </c>
       <c r="H29" s="26" t="n">
-        <v>44.76</v>
+        <v>37.86</v>
       </c>
       <c r="I29" s="26" t="n">
-        <v>31.7</v>
+        <v>23.5</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>10.85</v>
+        <v>-7.02</v>
       </c>
       <c r="K29" s="26" t="n">
-        <v>62.26</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-31.99</v>
+        <v>-32.52</v>
       </c>
       <c r="M29" s="26" t="n">
-        <v>14.99</v>
+        <v>14.49</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>57.02</v>
+        <v>52.44</v>
       </c>
       <c r="O29" s="26" t="n">
-        <v>-30.76</v>
+        <v>-27.46</v>
       </c>
       <c r="P29" s="26" t="n">
-        <v>17.99</v>
+        <v>24.59</v>
       </c>
       <c r="Q29" s="26" t="n">
-        <v>60.04</v>
+        <v>62.2</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>-25.43</v>
+        <v>-11.99</v>
       </c>
       <c r="S29" s="26" t="n">
-        <v>9.77</v>
+        <v>-2.84</v>
       </c>
       <c r="T29" s="26" t="n">
-        <v>49.33</v>
+        <v>65.44</v>
       </c>
       <c r="U29" s="26" t="n">
-        <v>-9.73</v>
+        <v>-18.71</v>
       </c>
       <c r="V29" s="26" t="n">
-        <v>-27.8</v>
+        <v>-17.73</v>
       </c>
       <c r="W29" s="26" t="n">
-        <v>41.86</v>
+        <v>44.6</v>
       </c>
       <c r="X29" s="26" t="n">
-        <v>-2.81</v>
+        <v>1.5</v>
       </c>
       <c r="Y29" s="26" t="n">
-        <v>-35.56</v>
+        <v>-40.54</v>
       </c>
       <c r="Z29" s="26" t="n">
-        <v>43.66</v>
+        <v>49.86</v>
       </c>
       <c r="AA29" s="26" t="n">
-        <v>-4.89</v>
+        <v>-3.78</v>
       </c>
       <c r="AB29" s="26" t="n">
-        <v>-30.71</v>
+        <v>-27.63</v>
       </c>
       <c r="AC29" s="26" t="n">
-        <v>53.2</v>
+        <v>61.32</v>
       </c>
       <c r="AD29" s="26" t="n">
-        <v>22.36</v>
+        <v>-5.57</v>
       </c>
       <c r="AE29" s="26" t="n">
-        <v>9.949999999999999</v>
+        <v>-15.02</v>
       </c>
       <c r="AF29" s="26" t="n">
-        <v>51.75</v>
+        <v>51.88</v>
       </c>
       <c r="AG29" s="26" t="n">
-        <v>30.75</v>
+        <v>22.59</v>
       </c>
       <c r="AH29" s="26" t="n">
-        <v>17.36</v>
+        <v>9.6</v>
       </c>
       <c r="AI29" s="26" t="n">
-        <v>65.06999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="AJ29" s="26" t="n">
-        <v>-25.03</v>
+        <v>-10.55</v>
       </c>
       <c r="AK29" s="26" t="n">
-        <v>5.82</v>
+        <v>-14.32</v>
       </c>
       <c r="AL29" s="26" t="n">
-        <v>63.38</v>
+        <v>64.48</v>
       </c>
       <c r="AM29" s="26" t="n">
-        <v>-29.98</v>
+        <v>-28.99</v>
       </c>
       <c r="AN29" s="26" t="n">
-        <v>14.33</v>
+        <v>15.19</v>
       </c>
       <c r="AO29" s="26" t="n">
-        <v>39.38</v>
+        <v>35.76</v>
       </c>
       <c r="AP29" s="26" t="n">
-        <v>-8.460000000000001</v>
+        <v>-17.28</v>
       </c>
       <c r="AQ29" s="26" t="n">
-        <v>-25.3</v>
+        <v>-17.87</v>
       </c>
       <c r="AR29" s="26" t="n">
-        <v>43.06</v>
+        <v>51.16</v>
       </c>
       <c r="AS29" s="26" t="n">
-        <v>-7.85</v>
+        <v>-11.52</v>
       </c>
       <c r="AT29" s="26" t="n">
-        <v>-29.94</v>
+        <v>-33.37</v>
       </c>
     </row>
     <row r="30">
@@ -16686,139 +16686,139 @@
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>46.16</v>
+        <v>43.54</v>
       </c>
       <c r="C30" s="26" t="n">
-        <v>30.74</v>
+        <v>20.96</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>11.98</v>
+        <v>-1.73</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>43.06</v>
+        <v>36.19</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>29.83</v>
+        <v>17.2</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>10.38</v>
+        <v>-7.11</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>45.32</v>
+        <v>39.53</v>
       </c>
       <c r="I30" s="26" t="n">
-        <v>31.84</v>
+        <v>23.91</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>9.109999999999999</v>
+        <v>-12.3</v>
       </c>
       <c r="K30" s="26" t="n">
-        <v>62.83</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-31.45</v>
+        <v>-30.88</v>
       </c>
       <c r="M30" s="26" t="n">
-        <v>14.26</v>
+        <v>12.27</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>57.21</v>
+        <v>53.02</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>-30.74</v>
+        <v>-27.42</v>
       </c>
       <c r="P30" s="26" t="n">
-        <v>18.09</v>
+        <v>24.89</v>
       </c>
       <c r="Q30" s="26" t="n">
-        <v>60.3</v>
+        <v>62.99</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>-24.98</v>
+        <v>-10.62</v>
       </c>
       <c r="S30" s="26" t="n">
-        <v>12.05</v>
+        <v>4.06</v>
       </c>
       <c r="T30" s="26" t="n">
-        <v>51</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="U30" s="26" t="n">
-        <v>-9.85</v>
+        <v>-19.09</v>
       </c>
       <c r="V30" s="26" t="n">
-        <v>-28.42</v>
+        <v>-19.62</v>
       </c>
       <c r="W30" s="26" t="n">
-        <v>42.02</v>
+        <v>45.09</v>
       </c>
       <c r="X30" s="26" t="n">
-        <v>-3.23</v>
+        <v>0.25</v>
       </c>
       <c r="Y30" s="26" t="n">
-        <v>-35.48</v>
+        <v>-40.31</v>
       </c>
       <c r="Z30" s="26" t="n">
-        <v>43.35</v>
+        <v>48.91</v>
       </c>
       <c r="AA30" s="26" t="n">
-        <v>-5.11</v>
+        <v>-4.43</v>
       </c>
       <c r="AB30" s="26" t="n">
-        <v>-31.92</v>
+        <v>-31.3</v>
       </c>
       <c r="AC30" s="26" t="n">
-        <v>53.19</v>
+        <v>61.3</v>
       </c>
       <c r="AD30" s="26" t="n">
-        <v>21.37</v>
+        <v>-8.57</v>
       </c>
       <c r="AE30" s="26" t="n">
-        <v>9.33</v>
+        <v>-16.92</v>
       </c>
       <c r="AF30" s="26" t="n">
-        <v>50.34</v>
+        <v>47.62</v>
       </c>
       <c r="AG30" s="26" t="n">
-        <v>30.72</v>
+        <v>22.49</v>
       </c>
       <c r="AH30" s="26" t="n">
-        <v>15.98</v>
+        <v>5.43</v>
       </c>
       <c r="AI30" s="26" t="n">
-        <v>64.42</v>
+        <v>73.78</v>
       </c>
       <c r="AJ30" s="26" t="n">
-        <v>-24.35</v>
+        <v>-8.48</v>
       </c>
       <c r="AK30" s="26" t="n">
-        <v>6.85</v>
+        <v>-11.19</v>
       </c>
       <c r="AL30" s="26" t="n">
-        <v>63.57</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="AM30" s="26" t="n">
-        <v>-29.85</v>
+        <v>-28.58</v>
       </c>
       <c r="AN30" s="26" t="n">
-        <v>14.23</v>
+        <v>14.88</v>
       </c>
       <c r="AO30" s="26" t="n">
-        <v>40.86</v>
+        <v>40.23</v>
       </c>
       <c r="AP30" s="26" t="n">
-        <v>-8.630000000000001</v>
+        <v>-17.79</v>
       </c>
       <c r="AQ30" s="26" t="n">
-        <v>-25.21</v>
+        <v>-17.61</v>
       </c>
       <c r="AR30" s="26" t="n">
-        <v>39.89</v>
+        <v>41.53</v>
       </c>
       <c r="AS30" s="26" t="n">
-        <v>-8.140000000000001</v>
+        <v>-12.41</v>
       </c>
       <c r="AT30" s="26" t="n">
-        <v>-31.02</v>
+        <v>-36.66</v>
       </c>
     </row>
     <row r="31">
@@ -16828,139 +16828,139 @@
         </is>
       </c>
       <c r="B31" s="26" t="n">
-        <v>46.6</v>
+        <v>44.86</v>
       </c>
       <c r="C31" s="26" t="n">
-        <v>30.97</v>
+        <v>21.66</v>
       </c>
       <c r="D31" s="26" t="n">
-        <v>11.65</v>
+        <v>-2.72</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>42.87</v>
+        <v>35.61</v>
       </c>
       <c r="F31" s="26" t="n">
-        <v>29.77</v>
+        <v>17.01</v>
       </c>
       <c r="G31" s="26" t="n">
-        <v>10.11</v>
+        <v>-7.95</v>
       </c>
       <c r="H31" s="26" t="n">
-        <v>44.88</v>
+        <v>38.2</v>
       </c>
       <c r="I31" s="26" t="n">
-        <v>30.74</v>
+        <v>20.57</v>
       </c>
       <c r="J31" s="26" t="n">
-        <v>9.359999999999999</v>
+        <v>-11.54</v>
       </c>
       <c r="K31" s="26" t="n">
-        <v>63.05</v>
+        <v>69.63</v>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-31.23</v>
+        <v>-30.22</v>
       </c>
       <c r="M31" s="26" t="n">
-        <v>14.31</v>
+        <v>12.42</v>
       </c>
       <c r="N31" s="26" t="n">
-        <v>56.98</v>
+        <v>52.32</v>
       </c>
       <c r="O31" s="26" t="n">
-        <v>-30.86</v>
+        <v>-27.77</v>
       </c>
       <c r="P31" s="26" t="n">
-        <v>17.63</v>
+        <v>23.5</v>
       </c>
       <c r="Q31" s="26" t="n">
-        <v>59.68</v>
+        <v>61.09</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>-24.74</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="S31" s="26" t="n">
-        <v>13.27</v>
+        <v>7.77</v>
       </c>
       <c r="T31" s="26" t="n">
-        <v>48.37</v>
+        <v>62.53</v>
       </c>
       <c r="U31" s="26" t="n">
-        <v>-9.07</v>
+        <v>-16.73</v>
       </c>
       <c r="V31" s="26" t="n">
-        <v>-28.86</v>
+        <v>-20.95</v>
       </c>
       <c r="W31" s="26" t="n">
-        <v>42.14</v>
+        <v>45.45</v>
       </c>
       <c r="X31" s="26" t="n">
-        <v>-3.21</v>
+        <v>0.31</v>
       </c>
       <c r="Y31" s="26" t="n">
-        <v>-35.12</v>
+        <v>-39.21</v>
       </c>
       <c r="Z31" s="26" t="n">
-        <v>43.71</v>
+        <v>50</v>
       </c>
       <c r="AA31" s="26" t="n">
-        <v>-4.13</v>
+        <v>-1.48</v>
       </c>
       <c r="AB31" s="26" t="n">
-        <v>-29.15</v>
+        <v>-22.9</v>
       </c>
       <c r="AC31" s="26" t="n">
-        <v>53.05</v>
+        <v>60.86</v>
       </c>
       <c r="AD31" s="26" t="n">
-        <v>20.92</v>
+        <v>-9.94</v>
       </c>
       <c r="AE31" s="26" t="n">
-        <v>6.44</v>
+        <v>-25.68</v>
       </c>
       <c r="AF31" s="26" t="n">
-        <v>50.41</v>
+        <v>47.81</v>
       </c>
       <c r="AG31" s="26" t="n">
-        <v>30.4</v>
+        <v>21.52</v>
       </c>
       <c r="AH31" s="26" t="n">
-        <v>18.78</v>
+        <v>13.89</v>
       </c>
       <c r="AI31" s="26" t="n">
-        <v>66.90000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="AJ31" s="26" t="n">
-        <v>-25.05</v>
+        <v>-10.59</v>
       </c>
       <c r="AK31" s="26" t="n">
-        <v>5.09</v>
+        <v>-16.54</v>
       </c>
       <c r="AL31" s="26" t="n">
-        <v>63.55</v>
+        <v>64.98</v>
       </c>
       <c r="AM31" s="26" t="n">
-        <v>-29.54</v>
+        <v>-27.65</v>
       </c>
       <c r="AN31" s="26" t="n">
-        <v>14.57</v>
+        <v>15.92</v>
       </c>
       <c r="AO31" s="26" t="n">
-        <v>41.28</v>
+        <v>41.49</v>
       </c>
       <c r="AP31" s="26" t="n">
-        <v>-7.28</v>
+        <v>-13.7</v>
       </c>
       <c r="AQ31" s="26" t="n">
-        <v>-24.42</v>
+        <v>-15.23</v>
       </c>
       <c r="AR31" s="26" t="n">
-        <v>43.91</v>
+        <v>53.73</v>
       </c>
       <c r="AS31" s="26" t="n">
-        <v>-8.130000000000001</v>
+        <v>-12.38</v>
       </c>
       <c r="AT31" s="26" t="n">
-        <v>-30.31</v>
+        <v>-34.49</v>
       </c>
     </row>
     <row r="32">
@@ -16970,139 +16970,139 @@
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>46.73</v>
+        <v>45.27</v>
       </c>
       <c r="C32" s="26" t="n">
-        <v>30.3</v>
+        <v>19.64</v>
       </c>
       <c r="D32" s="26" t="n">
-        <v>11.31</v>
+        <v>-3.78</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>42.72</v>
+        <v>35.14</v>
       </c>
       <c r="F32" s="26" t="n">
-        <v>29.43</v>
+        <v>15.98</v>
       </c>
       <c r="G32" s="26" t="n">
-        <v>10.02</v>
+        <v>-8.23</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>44.57</v>
+        <v>37.27</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>30.77</v>
+        <v>20.67</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>8.15</v>
+        <v>-15.2</v>
       </c>
       <c r="K32" s="26" t="n">
-        <v>62.57</v>
+        <v>68.16</v>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-31.13</v>
+        <v>-29.9</v>
       </c>
       <c r="M32" s="26" t="n">
-        <v>14.48</v>
+        <v>12.94</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>57.54</v>
+        <v>54.04</v>
       </c>
       <c r="O32" s="26" t="n">
-        <v>-31.02</v>
+        <v>-28.27</v>
       </c>
       <c r="P32" s="26" t="n">
-        <v>17.71</v>
+        <v>23.74</v>
       </c>
       <c r="Q32" s="26" t="n">
-        <v>60.59</v>
+        <v>63.86</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>-23.54</v>
+        <v>-6.26</v>
       </c>
       <c r="S32" s="26" t="n">
-        <v>9.529999999999999</v>
+        <v>-3.56</v>
       </c>
       <c r="T32" s="26" t="n">
-        <v>49.23</v>
+        <v>65.13</v>
       </c>
       <c r="U32" s="26" t="n">
-        <v>-10.15</v>
+        <v>-20</v>
       </c>
       <c r="V32" s="26" t="n">
-        <v>-29.43</v>
+        <v>-22.68</v>
       </c>
       <c r="W32" s="26" t="n">
-        <v>41.71</v>
+        <v>44.15</v>
       </c>
       <c r="X32" s="26" t="n">
-        <v>-2.84</v>
+        <v>1.41</v>
       </c>
       <c r="Y32" s="26" t="n">
-        <v>-35.56</v>
+        <v>-40.53</v>
       </c>
       <c r="Z32" s="26" t="n">
-        <v>43.66</v>
+        <v>49.87</v>
       </c>
       <c r="AA32" s="26" t="n">
-        <v>-5.41</v>
+        <v>-5.34</v>
       </c>
       <c r="AB32" s="26" t="n">
-        <v>-29.6</v>
+        <v>-24.28</v>
       </c>
       <c r="AC32" s="26" t="n">
-        <v>52.71</v>
+        <v>59.85</v>
       </c>
       <c r="AD32" s="26" t="n">
-        <v>20.79</v>
+        <v>-10.31</v>
       </c>
       <c r="AE32" s="26" t="n">
-        <v>8.17</v>
+        <v>-20.42</v>
       </c>
       <c r="AF32" s="26" t="n">
-        <v>51.21</v>
+        <v>50.24</v>
       </c>
       <c r="AG32" s="26" t="n">
-        <v>29.22</v>
+        <v>17.95</v>
       </c>
       <c r="AH32" s="26" t="n">
-        <v>16.73</v>
+        <v>7.7</v>
       </c>
       <c r="AI32" s="26" t="n">
-        <v>66.41</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="AJ32" s="26" t="n">
-        <v>-23.61</v>
+        <v>-6.23</v>
       </c>
       <c r="AK32" s="26" t="n">
-        <v>5.11</v>
+        <v>-16.47</v>
       </c>
       <c r="AL32" s="26" t="n">
-        <v>63.37</v>
+        <v>64.44</v>
       </c>
       <c r="AM32" s="26" t="n">
-        <v>-29.64</v>
+        <v>-27.96</v>
       </c>
       <c r="AN32" s="26" t="n">
-        <v>15</v>
+        <v>17.23</v>
       </c>
       <c r="AO32" s="26" t="n">
-        <v>40.56</v>
+        <v>39.33</v>
       </c>
       <c r="AP32" s="26" t="n">
-        <v>-7.92</v>
+        <v>-15.63</v>
       </c>
       <c r="AQ32" s="26" t="n">
-        <v>-24.49</v>
+        <v>-15.42</v>
       </c>
       <c r="AR32" s="26" t="n">
-        <v>42.51</v>
+        <v>49.49</v>
       </c>
       <c r="AS32" s="26" t="n">
-        <v>-7.57</v>
+        <v>-10.67</v>
       </c>
       <c r="AT32" s="26" t="n">
-        <v>-28.86</v>
+        <v>-30.11</v>
       </c>
     </row>
     <row r="33">
@@ -17112,139 +17112,139 @@
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>45.79</v>
+        <v>42.42</v>
       </c>
       <c r="C33" s="26" t="n">
-        <v>29.96</v>
+        <v>18.6</v>
       </c>
       <c r="D33" s="26" t="n">
-        <v>11.21</v>
+        <v>-4.07</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>42.58</v>
+        <v>34.72</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>29.26</v>
+        <v>15.48</v>
       </c>
       <c r="G33" s="26" t="n">
-        <v>10.35</v>
+        <v>-7.21</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>44.66</v>
+        <v>37.56</v>
       </c>
       <c r="I33" s="26" t="n">
-        <v>29.98</v>
+        <v>18.27</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>6.63</v>
+        <v>-19.81</v>
       </c>
       <c r="K33" s="26" t="n">
-        <v>63.37</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-31.46</v>
+        <v>-30.9</v>
       </c>
       <c r="M33" s="26" t="n">
-        <v>14.07</v>
+        <v>11.69</v>
       </c>
       <c r="N33" s="26" t="n">
-        <v>55.95</v>
+        <v>49.21</v>
       </c>
       <c r="O33" s="26" t="n">
-        <v>-30.19</v>
+        <v>-25.75</v>
       </c>
       <c r="P33" s="26" t="n">
-        <v>18.07</v>
+        <v>24.83</v>
       </c>
       <c r="Q33" s="26" t="n">
-        <v>61.98</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>-23.21</v>
+        <v>-5.24</v>
       </c>
       <c r="S33" s="26" t="n">
-        <v>11.76</v>
+        <v>3.2</v>
       </c>
       <c r="T33" s="26" t="n">
-        <v>50.2</v>
+        <v>68.08</v>
       </c>
       <c r="U33" s="26" t="n">
-        <v>-10.39</v>
+        <v>-20.73</v>
       </c>
       <c r="V33" s="26" t="n">
-        <v>-29.9</v>
+        <v>-24.11</v>
       </c>
       <c r="W33" s="26" t="n">
-        <v>42.36</v>
+        <v>46.11</v>
       </c>
       <c r="X33" s="26" t="n">
-        <v>-2.51</v>
+        <v>2.41</v>
       </c>
       <c r="Y33" s="26" t="n">
-        <v>-36.42</v>
+        <v>-43.15</v>
       </c>
       <c r="Z33" s="26" t="n">
-        <v>43.88</v>
+        <v>50.52</v>
       </c>
       <c r="AA33" s="26" t="n">
-        <v>-4.01</v>
+        <v>-1.12</v>
       </c>
       <c r="AB33" s="26" t="n">
-        <v>-28.59</v>
+        <v>-21.22</v>
       </c>
       <c r="AC33" s="26" t="n">
-        <v>53.12</v>
+        <v>61.1</v>
       </c>
       <c r="AD33" s="26" t="n">
-        <v>19.83</v>
+        <v>-13.22</v>
       </c>
       <c r="AE33" s="26" t="n">
-        <v>6.92</v>
+        <v>-24.22</v>
       </c>
       <c r="AF33" s="26" t="n">
-        <v>50.07</v>
+        <v>46.79</v>
       </c>
       <c r="AG33" s="26" t="n">
-        <v>30.2</v>
+        <v>20.9</v>
       </c>
       <c r="AH33" s="26" t="n">
-        <v>17.5</v>
+        <v>10.02</v>
       </c>
       <c r="AI33" s="26" t="n">
-        <v>64.86</v>
+        <v>75.12</v>
       </c>
       <c r="AJ33" s="26" t="n">
-        <v>-22.71</v>
+        <v>-3.52</v>
       </c>
       <c r="AK33" s="26" t="n">
-        <v>4.25</v>
+        <v>-19.1</v>
       </c>
       <c r="AL33" s="26" t="n">
-        <v>63.68</v>
+        <v>65.38</v>
       </c>
       <c r="AM33" s="26" t="n">
-        <v>-29.82</v>
+        <v>-28.51</v>
       </c>
       <c r="AN33" s="26" t="n">
-        <v>14.53</v>
+        <v>15.8</v>
       </c>
       <c r="AO33" s="26" t="n">
-        <v>40.27</v>
+        <v>38.44</v>
       </c>
       <c r="AP33" s="26" t="n">
-        <v>-9.82</v>
+        <v>-21.41</v>
       </c>
       <c r="AQ33" s="26" t="n">
-        <v>-22.63</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AR33" s="26" t="n">
-        <v>46.3</v>
+        <v>60.97</v>
       </c>
       <c r="AS33" s="26" t="n">
-        <v>-8.23</v>
+        <v>-12.66</v>
       </c>
       <c r="AT33" s="26" t="n">
-        <v>-31.1</v>
+        <v>-36.88</v>
       </c>
     </row>
     <row r="34">
@@ -17254,139 +17254,139 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>45.89</v>
+        <v>42.73</v>
       </c>
       <c r="C34" s="26" t="n">
-        <v>30.81</v>
+        <v>21.19</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>11.08</v>
+        <v>-4.47</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>42.08</v>
+        <v>33.22</v>
       </c>
       <c r="F34" s="26" t="n">
-        <v>29.04</v>
+        <v>14.8</v>
       </c>
       <c r="G34" s="26" t="n">
-        <v>9.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>45.06</v>
+        <v>38.74</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>30.41</v>
+        <v>19.6</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>8.289999999999999</v>
+        <v>-14.78</v>
       </c>
       <c r="K34" s="26" t="n">
-        <v>63.31</v>
+        <v>70.41</v>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-31.25</v>
+        <v>-30.28</v>
       </c>
       <c r="M34" s="26" t="n">
-        <v>14.26</v>
+        <v>12.25</v>
       </c>
       <c r="N34" s="26" t="n">
-        <v>56.92</v>
+        <v>52.14</v>
       </c>
       <c r="O34" s="26" t="n">
-        <v>-29.86</v>
+        <v>-24.76</v>
       </c>
       <c r="P34" s="26" t="n">
-        <v>17.79</v>
+        <v>23.98</v>
       </c>
       <c r="Q34" s="26" t="n">
-        <v>61.59</v>
+        <v>66.88</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>-23.16</v>
+        <v>-5.1</v>
       </c>
       <c r="S34" s="26" t="n">
-        <v>12.88</v>
+        <v>6.59</v>
       </c>
       <c r="T34" s="26" t="n">
-        <v>50.97</v>
+        <v>70.41</v>
       </c>
       <c r="U34" s="26" t="n">
-        <v>-9.77</v>
+        <v>-18.86</v>
       </c>
       <c r="V34" s="26" t="n">
-        <v>-27.44</v>
+        <v>-16.67</v>
       </c>
       <c r="W34" s="26" t="n">
-        <v>42.1</v>
+        <v>45.33</v>
       </c>
       <c r="X34" s="26" t="n">
-        <v>-2.64</v>
+        <v>2.04</v>
       </c>
       <c r="Y34" s="26" t="n">
-        <v>-36.17</v>
+        <v>-42.39</v>
       </c>
       <c r="Z34" s="26" t="n">
-        <v>43.99</v>
+        <v>50.86</v>
       </c>
       <c r="AA34" s="26" t="n">
-        <v>-3.89</v>
+        <v>-0.75</v>
       </c>
       <c r="AB34" s="26" t="n">
-        <v>-30.05</v>
+        <v>-25.65</v>
       </c>
       <c r="AC34" s="26" t="n">
-        <v>53.25</v>
+        <v>61.47</v>
       </c>
       <c r="AD34" s="26" t="n">
-        <v>19.63</v>
+        <v>-13.84</v>
       </c>
       <c r="AE34" s="26" t="n">
-        <v>5.78</v>
+        <v>-27.66</v>
       </c>
       <c r="AF34" s="26" t="n">
-        <v>50.53</v>
+        <v>48.19</v>
       </c>
       <c r="AG34" s="26" t="n">
-        <v>31.07</v>
+        <v>23.56</v>
       </c>
       <c r="AH34" s="26" t="n">
-        <v>16.15</v>
+        <v>5.93</v>
       </c>
       <c r="AI34" s="26" t="n">
-        <v>65.06</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AJ34" s="26" t="n">
-        <v>-23.85</v>
+        <v>-6.97</v>
       </c>
       <c r="AK34" s="26" t="n">
-        <v>5.12</v>
+        <v>-16.45</v>
       </c>
       <c r="AL34" s="26" t="n">
-        <v>63.73</v>
+        <v>65.53</v>
       </c>
       <c r="AM34" s="26" t="n">
-        <v>-29.68</v>
+        <v>-28.06</v>
       </c>
       <c r="AN34" s="26" t="n">
-        <v>14.81</v>
+        <v>16.65</v>
       </c>
       <c r="AO34" s="26" t="n">
-        <v>40.22</v>
+        <v>38.3</v>
       </c>
       <c r="AP34" s="26" t="n">
-        <v>-8.41</v>
+        <v>-17.13</v>
       </c>
       <c r="AQ34" s="26" t="n">
-        <v>-23.7</v>
+        <v>-13.02</v>
       </c>
       <c r="AR34" s="26" t="n">
-        <v>42.58</v>
+        <v>49.7</v>
       </c>
       <c r="AS34" s="26" t="n">
-        <v>-8.039999999999999</v>
+        <v>-12.12</v>
       </c>
       <c r="AT34" s="26" t="n">
-        <v>-30.83</v>
+        <v>-36.08</v>
       </c>
     </row>
     <row r="35">
